--- a/data/ch137_loyalty_program.xlsx
+++ b/data/ch137_loyalty_program.xlsx
@@ -471,7 +471,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>48.22</v>
+        <v>57.32</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>48.63</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="4">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>50.09</v>
+        <v>56.44</v>
       </c>
     </row>
     <row r="5">
@@ -543,7 +543,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>49.14</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>48.47</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>51.13</v>
+        <v>57.67</v>
       </c>
     </row>
     <row r="8">
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>49.52</v>
+        <v>57.97</v>
       </c>
     </row>
     <row r="9">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>47.13</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="10">
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>55.2</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="11">
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>54.72</v>
+        <v>55.53</v>
       </c>
     </row>
     <row r="12">
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>49.59</v>
+        <v>57.13</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>51.18</v>
+        <v>57.48</v>
       </c>
     </row>
     <row r="14">
@@ -759,7 +759,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>61.31</v>
       </c>
     </row>
     <row r="15">
@@ -783,7 +783,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>58.22</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="16">
@@ -807,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>51.28</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
@@ -831,7 +831,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="18">
@@ -855,7 +855,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>57.21</v>
+        <v>61.17</v>
       </c>
     </row>
     <row r="19">
@@ -879,7 +879,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>53.45</v>
+        <v>64.42</v>
       </c>
     </row>
     <row r="20">
@@ -903,7 +903,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="21">
@@ -927,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>56.88</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>56.78</v>
+        <v>65.95999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -975,7 +975,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>55.79</v>
+        <v>62.93</v>
       </c>
     </row>
     <row r="24">
@@ -999,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>60.17</v>
+        <v>60.83</v>
       </c>
     </row>
     <row r="25">
@@ -1023,7 +1023,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>57.09</v>
+        <v>63.97</v>
       </c>
     </row>
     <row r="26">
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>53.8</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="27">
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>55.05</v>
+        <v>55.01</v>
       </c>
     </row>
     <row r="28">
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>54.04</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="29">
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>57.18</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="30">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>55.98</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="31">
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>53.65</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="32">
@@ -1191,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>57.19</v>
+        <v>53.41</v>
       </c>
     </row>
     <row r="33">
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>61.27</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="34">
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>52.67</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="35">
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>56.19</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="36">
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>56.59</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="37">
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>56.35</v>
+        <v>50.48</v>
       </c>
     </row>
     <row r="38">
@@ -1335,7 +1335,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>62.78</v>
+        <v>57.11</v>
       </c>
     </row>
     <row r="39">
@@ -1359,7 +1359,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>60.77</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="40">
@@ -1383,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>63.03</v>
+        <v>59.13</v>
       </c>
     </row>
     <row r="41">
@@ -1407,7 +1407,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>62.82</v>
+        <v>60.22</v>
       </c>
     </row>
     <row r="42">
@@ -1431,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>59.76</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="43">
@@ -1455,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>59.74</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="44">
@@ -1479,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>65.72</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="45">
@@ -1503,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>61.97</v>
+        <v>61.96</v>
       </c>
     </row>
     <row r="46">
@@ -1527,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>62.75</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="47">
@@ -1551,7 +1551,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>65.86</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="48">
@@ -1575,7 +1575,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>64.28</v>
+        <v>57.26</v>
       </c>
     </row>
     <row r="49">
@@ -1599,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>61.89</v>
+        <v>59.61</v>
       </c>
     </row>
     <row r="50">
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>53.36</v>
+        <v>47.41</v>
       </c>
     </row>
     <row r="51">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>54.15</v>
+        <v>48.56</v>
       </c>
     </row>
     <row r="52">
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>50.93</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="53">
@@ -1695,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>54.47</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="54">
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>51.25</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="55">
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>52.59</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="56">
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>49.82</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="57">
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>52.16</v>
+        <v>49.66</v>
       </c>
     </row>
     <row r="58">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>53.8</v>
+        <v>48.42</v>
       </c>
     </row>
     <row r="59">
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>53.76</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="60">
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>54.69</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="61">
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>51.96</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="62">
@@ -1911,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>57.2</v>
+        <v>57.42</v>
       </c>
     </row>
     <row r="63">
@@ -1935,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>57.59</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="64">
@@ -1959,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>61.41</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="65">
@@ -1983,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>55.77</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="66">
@@ -2007,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>57.82</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="67">
@@ -2031,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>58.36</v>
+        <v>57.73</v>
       </c>
     </row>
     <row r="68">
@@ -2055,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>65.03</v>
+        <v>62.41</v>
       </c>
     </row>
     <row r="69">
@@ -2079,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>60.22</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="70">
@@ -2103,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>59.09</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="71">
@@ -2127,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>59.5</v>
+        <v>60.74</v>
       </c>
     </row>
     <row r="72">
@@ -2151,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>56.47</v>
+        <v>59.32</v>
       </c>
     </row>
     <row r="73">
@@ -2175,7 +2175,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>60.01</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="74">
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>55.69</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="75">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>55.31</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="76">
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>55.84</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="77">
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>58.32</v>
+        <v>55.28</v>
       </c>
     </row>
     <row r="78">
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>58.09</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="79">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>59.33</v>
+        <v>55.98</v>
       </c>
     </row>
     <row r="80">
@@ -2343,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>57.69</v>
+        <v>55.89</v>
       </c>
     </row>
     <row r="81">
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>58.97</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="82">
@@ -2391,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>55.9</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="83">
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>58.15</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="84">
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>55.84</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="85">
@@ -2463,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>57.01</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="86">
@@ -2487,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>60.71</v>
+        <v>63.11</v>
       </c>
     </row>
     <row r="87">
@@ -2511,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>62.43</v>
+        <v>59.36</v>
       </c>
     </row>
     <row r="88">
@@ -2535,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>65.04000000000001</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="89">
@@ -2559,7 +2559,7 @@
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>63.91</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="90">
@@ -2583,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>61.03</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="91">
@@ -2607,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>64.69</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="92">
@@ -2631,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>68.05</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="93">
@@ -2655,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>66.56</v>
+        <v>60.76</v>
       </c>
     </row>
     <row r="94">
@@ -2679,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>65.51000000000001</v>
+        <v>59.13</v>
       </c>
     </row>
     <row r="95">
@@ -2703,7 +2703,7 @@
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>66.69</v>
+        <v>62.32</v>
       </c>
     </row>
     <row r="96">
@@ -2727,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>66.94</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="97">
@@ -2751,7 +2751,7 @@
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>65.36</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="98">
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>55.35</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="99">
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>52.11</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="100">
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>54.16</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="101">
@@ -2847,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>51.8</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="102">
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>56.3</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="103">
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>46.17</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="104">
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>51.85</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="105">
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>46.65</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="106">
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>56.13</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="107">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>51.82</v>
+        <v>53.26</v>
       </c>
     </row>
     <row r="108">
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>55.71</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="109">
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>52.43</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="110">
@@ -3063,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>56.29</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="111">
@@ -3087,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>57</v>
+        <v>58.43</v>
       </c>
     </row>
     <row r="112">
@@ -3111,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>57.48</v>
+        <v>59.89</v>
       </c>
     </row>
     <row r="113">
@@ -3135,7 +3135,7 @@
         <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>60.69</v>
+        <v>58.98</v>
       </c>
     </row>
     <row r="114">
@@ -3159,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>57.01</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="115">
@@ -3183,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>54.88</v>
+        <v>59.96</v>
       </c>
     </row>
     <row r="116">
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>58.14</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="117">
@@ -3231,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>62.86</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="118">
@@ -3255,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>63.63</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="119">
@@ -3279,7 +3279,7 @@
         <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>59.58</v>
+        <v>57.56</v>
       </c>
     </row>
     <row r="120">
@@ -3303,7 +3303,7 @@
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>57.07</v>
+        <v>58.65</v>
       </c>
     </row>
     <row r="121">
@@ -3327,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>56.68</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="122">
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>52.99</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="123">
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>50.93</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="124">
@@ -3399,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>52.64</v>
+        <v>56.42</v>
       </c>
     </row>
     <row r="125">
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>55.15</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="126">
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>53.04</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="127">
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>52.9</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="128">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>54.94</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="129">
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>51.61</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="130">
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>54.44</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="131">
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>55.01</v>
+        <v>56.23</v>
       </c>
     </row>
     <row r="132">
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>54.55</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="133">
@@ -3615,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>54.14</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="134">
@@ -3639,7 +3639,7 @@
         <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>58.88</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="135">
@@ -3663,7 +3663,7 @@
         <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>61.33</v>
+        <v>59.66</v>
       </c>
     </row>
     <row r="136">
@@ -3687,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>54.52</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="137">
@@ -3711,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>61.48</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="138">
@@ -3735,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>59.62</v>
+        <v>58.39</v>
       </c>
     </row>
     <row r="139">
@@ -3759,7 +3759,7 @@
         <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>58.82</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="140">
@@ -3783,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>60.54</v>
+        <v>58.78</v>
       </c>
     </row>
     <row r="141">
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>61.57</v>
+        <v>60.84</v>
       </c>
     </row>
     <row r="142">
@@ -3831,7 +3831,7 @@
         <v>1</v>
       </c>
       <c r="F142" t="n">
-        <v>62.41</v>
+        <v>64.53</v>
       </c>
     </row>
     <row r="143">
@@ -3855,7 +3855,7 @@
         <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>59.95</v>
+        <v>58.66</v>
       </c>
     </row>
     <row r="144">
@@ -3879,7 +3879,7 @@
         <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>59.33</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="145">
@@ -3903,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="F145" t="n">
-        <v>61.28</v>
+        <v>57.61</v>
       </c>
     </row>
     <row r="146">
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>52.49</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="147">
@@ -3951,7 +3951,7 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>56.73</v>
+        <v>53.05</v>
       </c>
     </row>
     <row r="148">
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>47.75</v>
+        <v>54.02</v>
       </c>
     </row>
     <row r="149">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>53.11</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="150">
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>51.36</v>
+        <v>48.97</v>
       </c>
     </row>
     <row r="151">
@@ -4047,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>50.04</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="152">
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>52.22</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="153">
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>52.49</v>
+        <v>48.31</v>
       </c>
     </row>
     <row r="154">
@@ -4119,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>51.46</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="155">
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>49.71</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="156">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>51.47</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="157">
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>49.09</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="158">
@@ -4215,7 +4215,7 @@
         <v>1</v>
       </c>
       <c r="F158" t="n">
-        <v>56.88</v>
+        <v>57.49</v>
       </c>
     </row>
     <row r="159">
@@ -4239,7 +4239,7 @@
         <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>55.18</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="160">
@@ -4263,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="F160" t="n">
-        <v>58.03</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="161">
@@ -4287,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="F161" t="n">
-        <v>56.35</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="162">
@@ -4311,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="F162" t="n">
-        <v>56.07</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="163">
@@ -4335,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="F163" t="n">
-        <v>54.84</v>
+        <v>59.11</v>
       </c>
     </row>
     <row r="164">
@@ -4359,7 +4359,7 @@
         <v>1</v>
       </c>
       <c r="F164" t="n">
-        <v>57.87</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="165">
@@ -4383,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="F165" t="n">
-        <v>57.41</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="166">
@@ -4407,7 +4407,7 @@
         <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>56.55</v>
+        <v>58.88</v>
       </c>
     </row>
     <row r="167">
@@ -4431,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="F167" t="n">
-        <v>57.29</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="168">
@@ -4455,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="F168" t="n">
-        <v>59.48</v>
+        <v>60.57</v>
       </c>
     </row>
     <row r="169">
@@ -4479,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="F169" t="n">
-        <v>57.37</v>
+        <v>58.86</v>
       </c>
     </row>
     <row r="170">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>50.73</v>
+        <v>48.17</v>
       </c>
     </row>
     <row r="171">
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>50.02</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="172">
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>47.13</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="173">
@@ -4575,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>55.69</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="174">
@@ -4599,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>49.13</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="175">
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>50.25</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="176">
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>47.54</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="177">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>50.52</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="178">
@@ -4695,7 +4695,7 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>49.62</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="179">
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>50.14</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="180">
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>49.09</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="181">
@@ -4767,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>50.77</v>
+        <v>48.35</v>
       </c>
     </row>
     <row r="182">
@@ -4791,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="F182" t="n">
-        <v>54.69</v>
+        <v>50.79</v>
       </c>
     </row>
     <row r="183">
@@ -4815,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>54.7</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="184">
@@ -4839,7 +4839,7 @@
         <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>54.95</v>
+        <v>52.64</v>
       </c>
     </row>
     <row r="185">
@@ -4863,7 +4863,7 @@
         <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>53.84</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="186">
@@ -4887,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>52.75</v>
+        <v>56.71</v>
       </c>
     </row>
     <row r="187">
@@ -4911,7 +4911,7 @@
         <v>1</v>
       </c>
       <c r="F187" t="n">
-        <v>55.53</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="188">
@@ -4935,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="F188" t="n">
-        <v>60.65</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="189">
@@ -4959,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>58.24</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="190">
@@ -4983,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>56.41</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="191">
@@ -5007,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>55.13</v>
+        <v>61.46</v>
       </c>
     </row>
     <row r="192">
@@ -5031,7 +5031,7 @@
         <v>1</v>
       </c>
       <c r="F192" t="n">
-        <v>57.46</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="193">
@@ -5055,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="F193" t="n">
-        <v>58.06</v>
+        <v>60.02</v>
       </c>
     </row>
     <row r="194">
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>53.87</v>
+        <v>51.79</v>
       </c>
     </row>
     <row r="195">
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>51.49</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="196">
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>49.28</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="197">
@@ -5151,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>53.54</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="198">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>49.67</v>
+        <v>56.27</v>
       </c>
     </row>
     <row r="199">
@@ -5199,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>52.7</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="200">
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>47.91</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="201">
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>54.7</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="202">
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>51.35</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="203">
@@ -5295,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>52.06</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="204">
@@ -5319,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>52.85</v>
+        <v>57.81</v>
       </c>
     </row>
     <row r="205">
@@ -5343,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>51.57</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="206">
@@ -5367,7 +5367,7 @@
         <v>1</v>
       </c>
       <c r="F206" t="n">
-        <v>59.14</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="207">
@@ -5391,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="F207" t="n">
-        <v>58.23</v>
+        <v>64.14</v>
       </c>
     </row>
     <row r="208">
@@ -5415,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="F208" t="n">
-        <v>53.46</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="209">
@@ -5439,7 +5439,7 @@
         <v>1</v>
       </c>
       <c r="F209" t="n">
-        <v>61.33</v>
+        <v>59.32</v>
       </c>
     </row>
     <row r="210">
@@ -5463,7 +5463,7 @@
         <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>60.88</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="211">
@@ -5487,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="F211" t="n">
-        <v>59.21</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="212">
@@ -5511,7 +5511,7 @@
         <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>62.36</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="213">
@@ -5535,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="F213" t="n">
-        <v>60.72</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="214">
@@ -5559,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="F214" t="n">
-        <v>58.35</v>
+        <v>58.99</v>
       </c>
     </row>
     <row r="215">
@@ -5583,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="F215" t="n">
-        <v>60.92</v>
+        <v>59.87</v>
       </c>
     </row>
     <row r="216">
@@ -5607,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="F216" t="n">
-        <v>58.64</v>
+        <v>59.77</v>
       </c>
     </row>
     <row r="217">
@@ -5631,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="F217" t="n">
-        <v>58.53</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="218">
@@ -5655,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>48.33</v>
+        <v>56.27</v>
       </c>
     </row>
     <row r="219">
@@ -5679,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>52.55</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="220">
@@ -5703,7 +5703,7 @@
         <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>49.84</v>
+        <v>56.78</v>
       </c>
     </row>
     <row r="221">
@@ -5727,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>50.38</v>
+        <v>55.62</v>
       </c>
     </row>
     <row r="222">
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>51.06</v>
+        <v>54.04</v>
       </c>
     </row>
     <row r="223">
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>49.72</v>
+        <v>56.37</v>
       </c>
     </row>
     <row r="224">
@@ -5799,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="F224" t="n">
-        <v>52.36</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="225">
@@ -5823,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>50.34</v>
+        <v>54.89</v>
       </c>
     </row>
     <row r="226">
@@ -5847,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>52.81</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="227">
@@ -5871,7 +5871,7 @@
         <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>52.13</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="228">
@@ -5895,7 +5895,7 @@
         <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>51.15</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="229">
@@ -5919,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>52.62</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="230">
@@ -5943,7 +5943,7 @@
         <v>1</v>
       </c>
       <c r="F230" t="n">
-        <v>54.88</v>
+        <v>59.37</v>
       </c>
     </row>
     <row r="231">
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="F231" t="n">
-        <v>58.61</v>
+        <v>60.82</v>
       </c>
     </row>
     <row r="232">
@@ -5991,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="F232" t="n">
-        <v>58.19</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="233">
@@ -6015,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>55.48</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="234">
@@ -6039,7 +6039,7 @@
         <v>1</v>
       </c>
       <c r="F234" t="n">
-        <v>58.99</v>
+        <v>63.62</v>
       </c>
     </row>
     <row r="235">
@@ -6063,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="F235" t="n">
-        <v>58.13</v>
+        <v>62.88</v>
       </c>
     </row>
     <row r="236">
@@ -6087,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="F236" t="n">
-        <v>57.91</v>
+        <v>63.01</v>
       </c>
     </row>
     <row r="237">
@@ -6111,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="F237" t="n">
-        <v>62.72</v>
+        <v>62.31</v>
       </c>
     </row>
     <row r="238">
@@ -6135,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="F238" t="n">
-        <v>61.44</v>
+        <v>63.28</v>
       </c>
     </row>
     <row r="239">
@@ -6159,7 +6159,7 @@
         <v>1</v>
       </c>
       <c r="F239" t="n">
-        <v>60.02</v>
+        <v>62.09</v>
       </c>
     </row>
     <row r="240">
@@ -6183,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="F240" t="n">
-        <v>59.6</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="241">
@@ -6207,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="F241" t="n">
-        <v>58.14</v>
+        <v>63.98</v>
       </c>
     </row>
     <row r="242">
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>52.6</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="243">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>54.56</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="244">
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>53.39</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="245">
@@ -6303,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>50.57</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="246">
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>50.21</v>
+        <v>54.89</v>
       </c>
     </row>
     <row r="247">
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>51.87</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="248">
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>53.59</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="249">
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>56.82</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="250">
@@ -6423,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>50.34</v>
+        <v>56.44</v>
       </c>
     </row>
     <row r="251">
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>51.73</v>
+        <v>62.76</v>
       </c>
     </row>
     <row r="252">
@@ -6471,7 +6471,7 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>52.9</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="253">
@@ -6495,7 +6495,7 @@
         <v>0</v>
       </c>
       <c r="F253" t="n">
-        <v>54.76</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="254">
@@ -6519,7 +6519,7 @@
         <v>1</v>
       </c>
       <c r="F254" t="n">
-        <v>57.12</v>
+        <v>64.06999999999999</v>
       </c>
     </row>
     <row r="255">
@@ -6543,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="F255" t="n">
-        <v>60.09</v>
+        <v>64.27</v>
       </c>
     </row>
     <row r="256">
@@ -6567,7 +6567,7 @@
         <v>1</v>
       </c>
       <c r="F256" t="n">
-        <v>59.68</v>
+        <v>64.02</v>
       </c>
     </row>
     <row r="257">
@@ -6591,7 +6591,7 @@
         <v>1</v>
       </c>
       <c r="F257" t="n">
-        <v>59.21</v>
+        <v>65.33</v>
       </c>
     </row>
     <row r="258">
@@ -6615,7 +6615,7 @@
         <v>1</v>
       </c>
       <c r="F258" t="n">
-        <v>57.77</v>
+        <v>66.08</v>
       </c>
     </row>
     <row r="259">
@@ -6639,7 +6639,7 @@
         <v>1</v>
       </c>
       <c r="F259" t="n">
-        <v>60.22</v>
+        <v>63.62</v>
       </c>
     </row>
     <row r="260">
@@ -6663,7 +6663,7 @@
         <v>1</v>
       </c>
       <c r="F260" t="n">
-        <v>62.53</v>
+        <v>58.73</v>
       </c>
     </row>
     <row r="261">
@@ -6687,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="F261" t="n">
-        <v>62</v>
+        <v>60.22</v>
       </c>
     </row>
     <row r="262">
@@ -6711,7 +6711,7 @@
         <v>1</v>
       </c>
       <c r="F262" t="n">
-        <v>58.1</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="263">
@@ -6735,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="F263" t="n">
-        <v>58.36</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="264">
@@ -6759,7 +6759,7 @@
         <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>63.44</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="265">
@@ -6783,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>61.36</v>
+        <v>61.47</v>
       </c>
     </row>
     <row r="266">
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="F266" t="n">
-        <v>50.96</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="267">
@@ -6831,7 +6831,7 @@
         <v>0</v>
       </c>
       <c r="F267" t="n">
-        <v>52.25</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="268">
@@ -6855,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="F268" t="n">
-        <v>54.07</v>
+        <v>54.16</v>
       </c>
     </row>
     <row r="269">
@@ -6879,7 +6879,7 @@
         <v>0</v>
       </c>
       <c r="F269" t="n">
-        <v>51.61</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="270">
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>53.17</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="271">
@@ -6927,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="F271" t="n">
-        <v>52.34</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="272">
@@ -6951,7 +6951,7 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>51.65</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="273">
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>50.4</v>
+        <v>53.01</v>
       </c>
     </row>
     <row r="274">
@@ -6999,7 +6999,7 @@
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>51.71</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="275">
@@ -7023,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>55.09</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="276">
@@ -7047,7 +7047,7 @@
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>56.71</v>
+        <v>55.37</v>
       </c>
     </row>
     <row r="277">
@@ -7071,7 +7071,7 @@
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>50.77</v>
+        <v>56.78</v>
       </c>
     </row>
     <row r="278">
@@ -7095,7 +7095,7 @@
         <v>1</v>
       </c>
       <c r="F278" t="n">
-        <v>57.6</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="279">
@@ -7119,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="F279" t="n">
-        <v>60.65</v>
+        <v>60.05</v>
       </c>
     </row>
     <row r="280">
@@ -7143,7 +7143,7 @@
         <v>1</v>
       </c>
       <c r="F280" t="n">
-        <v>57.65</v>
+        <v>60.12</v>
       </c>
     </row>
     <row r="281">
@@ -7167,7 +7167,7 @@
         <v>1</v>
       </c>
       <c r="F281" t="n">
-        <v>58.71</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="282">
@@ -7191,7 +7191,7 @@
         <v>1</v>
       </c>
       <c r="F282" t="n">
-        <v>58.05</v>
+        <v>57.54</v>
       </c>
     </row>
     <row r="283">
@@ -7215,7 +7215,7 @@
         <v>1</v>
       </c>
       <c r="F283" t="n">
-        <v>63.1</v>
+        <v>62.94</v>
       </c>
     </row>
     <row r="284">
@@ -7239,7 +7239,7 @@
         <v>1</v>
       </c>
       <c r="F284" t="n">
-        <v>57</v>
+        <v>64.56999999999999</v>
       </c>
     </row>
     <row r="285">
@@ -7263,7 +7263,7 @@
         <v>1</v>
       </c>
       <c r="F285" t="n">
-        <v>58.13</v>
+        <v>64.73</v>
       </c>
     </row>
     <row r="286">
@@ -7287,7 +7287,7 @@
         <v>1</v>
       </c>
       <c r="F286" t="n">
-        <v>62.9</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="287">
@@ -7311,7 +7311,7 @@
         <v>1</v>
       </c>
       <c r="F287" t="n">
-        <v>60.52</v>
+        <v>66.36</v>
       </c>
     </row>
     <row r="288">
@@ -7335,7 +7335,7 @@
         <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>58.39</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="289">
@@ -7359,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>62.67</v>
+        <v>63.47</v>
       </c>
     </row>
     <row r="290">
@@ -7383,7 +7383,7 @@
         <v>0</v>
       </c>
       <c r="F290" t="n">
-        <v>55.61</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="291">
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="F291" t="n">
-        <v>55.89</v>
+        <v>55.95</v>
       </c>
     </row>
     <row r="292">
@@ -7431,7 +7431,7 @@
         <v>0</v>
       </c>
       <c r="F292" t="n">
-        <v>53.76</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="293">
@@ -7455,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="F293" t="n">
-        <v>52.99</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="294">
@@ -7479,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="F294" t="n">
-        <v>52.99</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="295">
@@ -7503,7 +7503,7 @@
         <v>0</v>
       </c>
       <c r="F295" t="n">
-        <v>49.83</v>
+        <v>48.77</v>
       </c>
     </row>
     <row r="296">
@@ -7527,7 +7527,7 @@
         <v>0</v>
       </c>
       <c r="F296" t="n">
-        <v>55.91</v>
+        <v>52.13</v>
       </c>
     </row>
     <row r="297">
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="F297" t="n">
-        <v>53.42</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="298">
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="F298" t="n">
-        <v>56.72</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="299">
@@ -7599,7 +7599,7 @@
         <v>0</v>
       </c>
       <c r="F299" t="n">
-        <v>54.51</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="300">
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="F300" t="n">
-        <v>51.65</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="301">
@@ -7647,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>54.04</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="302">
@@ -7671,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>57.75</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="303">
@@ -7695,7 +7695,7 @@
         <v>1</v>
       </c>
       <c r="F303" t="n">
-        <v>61.58</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="304">
@@ -7719,7 +7719,7 @@
         <v>1</v>
       </c>
       <c r="F304" t="n">
-        <v>61.66</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="305">
@@ -7743,7 +7743,7 @@
         <v>1</v>
       </c>
       <c r="F305" t="n">
-        <v>62.41</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="306">
@@ -7767,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="F306" t="n">
-        <v>59.32</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="307">
@@ -7791,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="F307" t="n">
-        <v>61.84</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="308">
@@ -7815,7 +7815,7 @@
         <v>1</v>
       </c>
       <c r="F308" t="n">
-        <v>62.77</v>
+        <v>61.07</v>
       </c>
     </row>
     <row r="309">
@@ -7839,7 +7839,7 @@
         <v>1</v>
       </c>
       <c r="F309" t="n">
-        <v>58.76</v>
+        <v>62.92</v>
       </c>
     </row>
     <row r="310">
@@ -7863,7 +7863,7 @@
         <v>1</v>
       </c>
       <c r="F310" t="n">
-        <v>62.9</v>
+        <v>63.31</v>
       </c>
     </row>
     <row r="311">
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="F311" t="n">
-        <v>62.52</v>
+        <v>65.13</v>
       </c>
     </row>
     <row r="312">
@@ -7911,7 +7911,7 @@
         <v>1</v>
       </c>
       <c r="F312" t="n">
-        <v>57.72</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="313">
@@ -7935,7 +7935,7 @@
         <v>1</v>
       </c>
       <c r="F313" t="n">
-        <v>63.29</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="314">
@@ -7959,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="F314" t="n">
-        <v>55.76</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="315">
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="F315" t="n">
-        <v>59.75</v>
+        <v>48.28</v>
       </c>
     </row>
     <row r="316">
@@ -8007,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="F316" t="n">
-        <v>54.58</v>
+        <v>51.39</v>
       </c>
     </row>
     <row r="317">
@@ -8031,7 +8031,7 @@
         <v>0</v>
       </c>
       <c r="F317" t="n">
-        <v>52.93</v>
+        <v>49.96</v>
       </c>
     </row>
     <row r="318">
@@ -8055,7 +8055,7 @@
         <v>0</v>
       </c>
       <c r="F318" t="n">
-        <v>51.8</v>
+        <v>50.36</v>
       </c>
     </row>
     <row r="319">
@@ -8079,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="F319" t="n">
-        <v>53.8</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="320">
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="F320" t="n">
-        <v>55.58</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="321">
@@ -8127,7 +8127,7 @@
         <v>0</v>
       </c>
       <c r="F321" t="n">
-        <v>55.86</v>
+        <v>57.43</v>
       </c>
     </row>
     <row r="322">
@@ -8151,7 +8151,7 @@
         <v>0</v>
       </c>
       <c r="F322" t="n">
-        <v>55.62</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="323">
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="F323" t="n">
-        <v>60.86</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="324">
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="F324" t="n">
-        <v>58.08</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="325">
@@ -8223,7 +8223,7 @@
         <v>0</v>
       </c>
       <c r="F325" t="n">
-        <v>56</v>
+        <v>52.05</v>
       </c>
     </row>
     <row r="326">
@@ -8247,7 +8247,7 @@
         <v>1</v>
       </c>
       <c r="F326" t="n">
-        <v>58.86</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="327">
@@ -8271,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="F327" t="n">
-        <v>61.11</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="328">
@@ -8295,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="F328" t="n">
-        <v>60.11</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="329">
@@ -8319,7 +8319,7 @@
         <v>1</v>
       </c>
       <c r="F329" t="n">
-        <v>59.18</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="330">
@@ -8343,7 +8343,7 @@
         <v>1</v>
       </c>
       <c r="F330" t="n">
-        <v>59.55</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="331">
@@ -8367,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="F331" t="n">
-        <v>63.11</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="332">
@@ -8391,7 +8391,7 @@
         <v>1</v>
       </c>
       <c r="F332" t="n">
-        <v>57.91</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="333">
@@ -8415,7 +8415,7 @@
         <v>1</v>
       </c>
       <c r="F333" t="n">
-        <v>60.99</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="334">
@@ -8439,7 +8439,7 @@
         <v>1</v>
       </c>
       <c r="F334" t="n">
-        <v>60.89</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="335">
@@ -8463,7 +8463,7 @@
         <v>1</v>
       </c>
       <c r="F335" t="n">
-        <v>65.34999999999999</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="336">
@@ -8487,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="F336" t="n">
-        <v>62.85</v>
+        <v>61.24</v>
       </c>
     </row>
     <row r="337">
@@ -8511,7 +8511,7 @@
         <v>1</v>
       </c>
       <c r="F337" t="n">
-        <v>63.28</v>
+        <v>63.19</v>
       </c>
     </row>
     <row r="338">
@@ -8535,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="F338" t="n">
-        <v>50.18</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="339">
@@ -8559,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="F339" t="n">
-        <v>51.31</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="340">
@@ -8583,7 +8583,7 @@
         <v>0</v>
       </c>
       <c r="F340" t="n">
-        <v>49.81</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="341">
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="F341" t="n">
-        <v>46.47</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="342">
@@ -8631,7 +8631,7 @@
         <v>0</v>
       </c>
       <c r="F342" t="n">
-        <v>53.99</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="343">
@@ -8655,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="F343" t="n">
-        <v>48.94</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="344">
@@ -8679,7 +8679,7 @@
         <v>0</v>
       </c>
       <c r="F344" t="n">
-        <v>48.56</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="345">
@@ -8703,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="F345" t="n">
-        <v>53.11</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="346">
@@ -8727,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="F346" t="n">
-        <v>50.58</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="347">
@@ -8751,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="F347" t="n">
-        <v>52.46</v>
+        <v>51.13</v>
       </c>
     </row>
     <row r="348">
@@ -8775,7 +8775,7 @@
         <v>0</v>
       </c>
       <c r="F348" t="n">
-        <v>54.24</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="349">
@@ -8799,7 +8799,7 @@
         <v>0</v>
       </c>
       <c r="F349" t="n">
-        <v>52.67</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="350">
@@ -8823,7 +8823,7 @@
         <v>1</v>
       </c>
       <c r="F350" t="n">
-        <v>58.51</v>
+        <v>53.56</v>
       </c>
     </row>
     <row r="351">
@@ -8847,7 +8847,7 @@
         <v>1</v>
       </c>
       <c r="F351" t="n">
-        <v>54.25</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="352">
@@ -8871,7 +8871,7 @@
         <v>1</v>
       </c>
       <c r="F352" t="n">
-        <v>54.55</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="353">
@@ -8895,7 +8895,7 @@
         <v>1</v>
       </c>
       <c r="F353" t="n">
-        <v>58.09</v>
+        <v>57.41</v>
       </c>
     </row>
     <row r="354">
@@ -8919,7 +8919,7 @@
         <v>1</v>
       </c>
       <c r="F354" t="n">
-        <v>55.42</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="355">
@@ -8943,7 +8943,7 @@
         <v>1</v>
       </c>
       <c r="F355" t="n">
-        <v>58.77</v>
+        <v>55.75</v>
       </c>
     </row>
     <row r="356">
@@ -8967,7 +8967,7 @@
         <v>1</v>
       </c>
       <c r="F356" t="n">
-        <v>59.54</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="357">
@@ -8991,7 +8991,7 @@
         <v>1</v>
       </c>
       <c r="F357" t="n">
-        <v>61.87</v>
+        <v>55.97</v>
       </c>
     </row>
     <row r="358">
@@ -9015,7 +9015,7 @@
         <v>1</v>
       </c>
       <c r="F358" t="n">
-        <v>58.96</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="359">
@@ -9039,7 +9039,7 @@
         <v>1</v>
       </c>
       <c r="F359" t="n">
-        <v>61.6</v>
+        <v>53.94</v>
       </c>
     </row>
     <row r="360">
@@ -9063,7 +9063,7 @@
         <v>1</v>
       </c>
       <c r="F360" t="n">
-        <v>62.93</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="361">
@@ -9087,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="F361" t="n">
-        <v>60.87</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="362">
@@ -9111,7 +9111,7 @@
         <v>0</v>
       </c>
       <c r="F362" t="n">
-        <v>53.9</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="363">
@@ -9135,7 +9135,7 @@
         <v>0</v>
       </c>
       <c r="F363" t="n">
-        <v>57.51</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="364">
@@ -9159,7 +9159,7 @@
         <v>0</v>
       </c>
       <c r="F364" t="n">
-        <v>54.32</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="365">
@@ -9183,7 +9183,7 @@
         <v>0</v>
       </c>
       <c r="F365" t="n">
-        <v>53.21</v>
+        <v>50.36</v>
       </c>
     </row>
     <row r="366">
@@ -9207,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="F366" t="n">
-        <v>56.79</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="367">
@@ -9231,7 +9231,7 @@
         <v>0</v>
       </c>
       <c r="F367" t="n">
-        <v>52.7</v>
+        <v>52.08</v>
       </c>
     </row>
     <row r="368">
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="F368" t="n">
-        <v>55.57</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="369">
@@ -9279,7 +9279,7 @@
         <v>0</v>
       </c>
       <c r="F369" t="n">
-        <v>55.85</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="370">
@@ -9303,7 +9303,7 @@
         <v>0</v>
       </c>
       <c r="F370" t="n">
-        <v>55.44</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="371">
@@ -9327,7 +9327,7 @@
         <v>0</v>
       </c>
       <c r="F371" t="n">
-        <v>55.3</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="372">
@@ -9351,7 +9351,7 @@
         <v>0</v>
       </c>
       <c r="F372" t="n">
-        <v>56.26</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="373">
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="F373" t="n">
-        <v>52.81</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="374">
@@ -9399,7 +9399,7 @@
         <v>1</v>
       </c>
       <c r="F374" t="n">
-        <v>57.58</v>
+        <v>62.01</v>
       </c>
     </row>
     <row r="375">
@@ -9423,7 +9423,7 @@
         <v>1</v>
       </c>
       <c r="F375" t="n">
-        <v>59.89</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="376">
@@ -9447,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="F376" t="n">
-        <v>63.02</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="377">
@@ -9471,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="F377" t="n">
-        <v>63.2</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="378">
@@ -9495,7 +9495,7 @@
         <v>1</v>
       </c>
       <c r="F378" t="n">
-        <v>64.92</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="379">
@@ -9519,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="F379" t="n">
-        <v>60.73</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="380">
@@ -9543,7 +9543,7 @@
         <v>1</v>
       </c>
       <c r="F380" t="n">
-        <v>61.67</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="381">
@@ -9567,7 +9567,7 @@
         <v>1</v>
       </c>
       <c r="F381" t="n">
-        <v>60.14</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="382">
@@ -9591,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="F382" t="n">
-        <v>62.28</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="383">
@@ -9615,7 +9615,7 @@
         <v>1</v>
       </c>
       <c r="F383" t="n">
-        <v>59.51</v>
+        <v>64.70999999999999</v>
       </c>
     </row>
     <row r="384">
@@ -9639,7 +9639,7 @@
         <v>1</v>
       </c>
       <c r="F384" t="n">
-        <v>61.16</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="385">
@@ -9663,7 +9663,7 @@
         <v>1</v>
       </c>
       <c r="F385" t="n">
-        <v>61.62</v>
+        <v>66.42</v>
       </c>
     </row>
     <row r="386">
@@ -9687,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="F386" t="n">
-        <v>47.76</v>
+        <v>56.11</v>
       </c>
     </row>
     <row r="387">
@@ -9711,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="F387" t="n">
-        <v>47.33</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="388">
@@ -9735,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="F388" t="n">
-        <v>53.21</v>
+        <v>60.33</v>
       </c>
     </row>
     <row r="389">
@@ -9759,7 +9759,7 @@
         <v>0</v>
       </c>
       <c r="F389" t="n">
-        <v>52.19</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="390">
@@ -9783,7 +9783,7 @@
         <v>0</v>
       </c>
       <c r="F390" t="n">
-        <v>52.34</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="391">
@@ -9807,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="F391" t="n">
-        <v>54.43</v>
+        <v>61.13</v>
       </c>
     </row>
     <row r="392">
@@ -9831,7 +9831,7 @@
         <v>0</v>
       </c>
       <c r="F392" t="n">
-        <v>51.26</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="393">
@@ -9855,7 +9855,7 @@
         <v>0</v>
       </c>
       <c r="F393" t="n">
-        <v>53.55</v>
+        <v>59.64</v>
       </c>
     </row>
     <row r="394">
@@ -9879,7 +9879,7 @@
         <v>0</v>
       </c>
       <c r="F394" t="n">
-        <v>52.36</v>
+        <v>60.17</v>
       </c>
     </row>
     <row r="395">
@@ -9903,7 +9903,7 @@
         <v>0</v>
       </c>
       <c r="F395" t="n">
-        <v>55.6</v>
+        <v>60.92</v>
       </c>
     </row>
     <row r="396">
@@ -9927,7 +9927,7 @@
         <v>0</v>
       </c>
       <c r="F396" t="n">
-        <v>51.84</v>
+        <v>62.72</v>
       </c>
     </row>
     <row r="397">
@@ -9951,7 +9951,7 @@
         <v>0</v>
       </c>
       <c r="F397" t="n">
-        <v>52.51</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="398">
@@ -9975,7 +9975,7 @@
         <v>1</v>
       </c>
       <c r="F398" t="n">
-        <v>60.56</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="399">
@@ -9999,7 +9999,7 @@
         <v>1</v>
       </c>
       <c r="F399" t="n">
-        <v>58.82</v>
+        <v>70.17</v>
       </c>
     </row>
     <row r="400">
@@ -10023,7 +10023,7 @@
         <v>1</v>
       </c>
       <c r="F400" t="n">
-        <v>54.17</v>
+        <v>69.15000000000001</v>
       </c>
     </row>
     <row r="401">
@@ -10047,7 +10047,7 @@
         <v>1</v>
       </c>
       <c r="F401" t="n">
-        <v>56.35</v>
+        <v>63.98</v>
       </c>
     </row>
     <row r="402">
@@ -10071,7 +10071,7 @@
         <v>1</v>
       </c>
       <c r="F402" t="n">
-        <v>58.3</v>
+        <v>64.73999999999999</v>
       </c>
     </row>
     <row r="403">
@@ -10095,7 +10095,7 @@
         <v>1</v>
       </c>
       <c r="F403" t="n">
-        <v>61.02</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="404">
@@ -10119,7 +10119,7 @@
         <v>1</v>
       </c>
       <c r="F404" t="n">
-        <v>56.13</v>
+        <v>66.13</v>
       </c>
     </row>
     <row r="405">
@@ -10143,7 +10143,7 @@
         <v>1</v>
       </c>
       <c r="F405" t="n">
-        <v>60.26</v>
+        <v>65.01000000000001</v>
       </c>
     </row>
     <row r="406">
@@ -10167,7 +10167,7 @@
         <v>1</v>
       </c>
       <c r="F406" t="n">
-        <v>54.69</v>
+        <v>69.34999999999999</v>
       </c>
     </row>
     <row r="407">
@@ -10191,7 +10191,7 @@
         <v>1</v>
       </c>
       <c r="F407" t="n">
-        <v>54.57</v>
+        <v>68.54000000000001</v>
       </c>
     </row>
     <row r="408">
@@ -10215,7 +10215,7 @@
         <v>1</v>
       </c>
       <c r="F408" t="n">
-        <v>60.85</v>
+        <v>66.68000000000001</v>
       </c>
     </row>
     <row r="409">
@@ -10239,7 +10239,7 @@
         <v>1</v>
       </c>
       <c r="F409" t="n">
-        <v>58.05</v>
+        <v>68.70999999999999</v>
       </c>
     </row>
     <row r="410">
@@ -10263,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="F410" t="n">
-        <v>51.45</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="411">
@@ -10287,7 +10287,7 @@
         <v>0</v>
       </c>
       <c r="F411" t="n">
-        <v>49.37</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="412">
@@ -10311,7 +10311,7 @@
         <v>0</v>
       </c>
       <c r="F412" t="n">
-        <v>53.44</v>
+        <v>57.32</v>
       </c>
     </row>
     <row r="413">
@@ -10335,7 +10335,7 @@
         <v>0</v>
       </c>
       <c r="F413" t="n">
-        <v>48.98</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="414">
@@ -10359,7 +10359,7 @@
         <v>0</v>
       </c>
       <c r="F414" t="n">
-        <v>50.39</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="415">
@@ -10383,7 +10383,7 @@
         <v>0</v>
       </c>
       <c r="F415" t="n">
-        <v>51.11</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="416">
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="F416" t="n">
-        <v>51.97</v>
+        <v>56.51</v>
       </c>
     </row>
     <row r="417">
@@ -10431,7 +10431,7 @@
         <v>0</v>
       </c>
       <c r="F417" t="n">
-        <v>51.01</v>
+        <v>54.69</v>
       </c>
     </row>
     <row r="418">
@@ -10455,7 +10455,7 @@
         <v>0</v>
       </c>
       <c r="F418" t="n">
-        <v>53.66</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="419">
@@ -10479,7 +10479,7 @@
         <v>0</v>
       </c>
       <c r="F419" t="n">
-        <v>52.11</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="420">
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="F420" t="n">
-        <v>49.54</v>
+        <v>55.98</v>
       </c>
     </row>
     <row r="421">
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="F421" t="n">
-        <v>53.85</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="422">
@@ -10551,7 +10551,7 @@
         <v>1</v>
       </c>
       <c r="F422" t="n">
-        <v>57.79</v>
+        <v>59.02</v>
       </c>
     </row>
     <row r="423">
@@ -10575,7 +10575,7 @@
         <v>1</v>
       </c>
       <c r="F423" t="n">
-        <v>57.88</v>
+        <v>58.86</v>
       </c>
     </row>
     <row r="424">
@@ -10599,7 +10599,7 @@
         <v>1</v>
       </c>
       <c r="F424" t="n">
-        <v>58.66</v>
+        <v>60.84</v>
       </c>
     </row>
     <row r="425">
@@ -10623,7 +10623,7 @@
         <v>1</v>
       </c>
       <c r="F425" t="n">
-        <v>56.37</v>
+        <v>60.22</v>
       </c>
     </row>
     <row r="426">
@@ -10647,7 +10647,7 @@
         <v>1</v>
       </c>
       <c r="F426" t="n">
-        <v>58.07</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="427">
@@ -10671,7 +10671,7 @@
         <v>1</v>
       </c>
       <c r="F427" t="n">
-        <v>57.24</v>
+        <v>65.26000000000001</v>
       </c>
     </row>
     <row r="428">
@@ -10695,7 +10695,7 @@
         <v>1</v>
       </c>
       <c r="F428" t="n">
-        <v>62.55</v>
+        <v>63.52</v>
       </c>
     </row>
     <row r="429">
@@ -10719,7 +10719,7 @@
         <v>1</v>
       </c>
       <c r="F429" t="n">
-        <v>59.81</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="430">
@@ -10743,7 +10743,7 @@
         <v>1</v>
       </c>
       <c r="F430" t="n">
-        <v>59.05</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="431">
@@ -10767,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="F431" t="n">
-        <v>58.32</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="432">
@@ -10791,7 +10791,7 @@
         <v>1</v>
       </c>
       <c r="F432" t="n">
-        <v>62.1</v>
+        <v>62.46</v>
       </c>
     </row>
     <row r="433">
@@ -10815,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="F433" t="n">
-        <v>57.58</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="434">
@@ -10839,7 +10839,7 @@
         <v>0</v>
       </c>
       <c r="F434" t="n">
-        <v>50.31</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="435">
@@ -10863,7 +10863,7 @@
         <v>0</v>
       </c>
       <c r="F435" t="n">
-        <v>48.58</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="436">
@@ -10887,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="F436" t="n">
-        <v>50.02</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="437">
@@ -10911,7 +10911,7 @@
         <v>0</v>
       </c>
       <c r="F437" t="n">
-        <v>48.48</v>
+        <v>47.88</v>
       </c>
     </row>
     <row r="438">
@@ -10935,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="F438" t="n">
-        <v>54.04</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="439">
@@ -10959,7 +10959,7 @@
         <v>0</v>
       </c>
       <c r="F439" t="n">
-        <v>54.13</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="440">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="F440" t="n">
-        <v>50.53</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="441">
@@ -11007,7 +11007,7 @@
         <v>0</v>
       </c>
       <c r="F441" t="n">
-        <v>53.98</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="442">
@@ -11031,7 +11031,7 @@
         <v>0</v>
       </c>
       <c r="F442" t="n">
-        <v>54.38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="443">
@@ -11055,7 +11055,7 @@
         <v>0</v>
       </c>
       <c r="F443" t="n">
-        <v>53.66</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="444">
@@ -11079,7 +11079,7 @@
         <v>0</v>
       </c>
       <c r="F444" t="n">
-        <v>52.72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="445">
@@ -11103,7 +11103,7 @@
         <v>0</v>
       </c>
       <c r="F445" t="n">
-        <v>52.61</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="446">
@@ -11127,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="F446" t="n">
-        <v>56.85</v>
+        <v>59.93</v>
       </c>
     </row>
     <row r="447">
@@ -11151,7 +11151,7 @@
         <v>1</v>
       </c>
       <c r="F447" t="n">
-        <v>59.98</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="448">
@@ -11175,7 +11175,7 @@
         <v>1</v>
       </c>
       <c r="F448" t="n">
-        <v>60.33</v>
+        <v>54.59</v>
       </c>
     </row>
     <row r="449">
@@ -11199,7 +11199,7 @@
         <v>1</v>
       </c>
       <c r="F449" t="n">
-        <v>61.51</v>
+        <v>53.49</v>
       </c>
     </row>
     <row r="450">
@@ -11223,7 +11223,7 @@
         <v>1</v>
       </c>
       <c r="F450" t="n">
-        <v>58.51</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="451">
@@ -11247,7 +11247,7 @@
         <v>1</v>
       </c>
       <c r="F451" t="n">
-        <v>58.89</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="452">
@@ -11271,7 +11271,7 @@
         <v>1</v>
       </c>
       <c r="F452" t="n">
-        <v>58.37</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="453">
@@ -11295,7 +11295,7 @@
         <v>1</v>
       </c>
       <c r="F453" t="n">
-        <v>60.82</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="454">
@@ -11319,7 +11319,7 @@
         <v>1</v>
       </c>
       <c r="F454" t="n">
-        <v>61.56</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="455">
@@ -11343,7 +11343,7 @@
         <v>1</v>
       </c>
       <c r="F455" t="n">
-        <v>61.29</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="456">
@@ -11367,7 +11367,7 @@
         <v>1</v>
       </c>
       <c r="F456" t="n">
-        <v>58.62</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="457">
@@ -11391,7 +11391,7 @@
         <v>1</v>
       </c>
       <c r="F457" t="n">
-        <v>56.09</v>
+        <v>61.09</v>
       </c>
     </row>
     <row r="458">
@@ -11415,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="F458" t="n">
-        <v>56.14</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="459">
@@ -11439,7 +11439,7 @@
         <v>0</v>
       </c>
       <c r="F459" t="n">
-        <v>57.31</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="460">
@@ -11463,7 +11463,7 @@
         <v>0</v>
       </c>
       <c r="F460" t="n">
-        <v>60.99</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="461">
@@ -11487,7 +11487,7 @@
         <v>0</v>
       </c>
       <c r="F461" t="n">
-        <v>60.2</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="462">
@@ -11511,7 +11511,7 @@
         <v>0</v>
       </c>
       <c r="F462" t="n">
-        <v>58.67</v>
+        <v>48.07</v>
       </c>
     </row>
     <row r="463">
@@ -11535,7 +11535,7 @@
         <v>0</v>
       </c>
       <c r="F463" t="n">
-        <v>58.73</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="464">
@@ -11559,7 +11559,7 @@
         <v>0</v>
       </c>
       <c r="F464" t="n">
-        <v>58.22</v>
+        <v>47.98</v>
       </c>
     </row>
     <row r="465">
@@ -11583,7 +11583,7 @@
         <v>0</v>
       </c>
       <c r="F465" t="n">
-        <v>56.8</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="466">
@@ -11607,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="F466" t="n">
-        <v>60.21</v>
+        <v>51.04</v>
       </c>
     </row>
     <row r="467">
@@ -11631,7 +11631,7 @@
         <v>0</v>
       </c>
       <c r="F467" t="n">
-        <v>59.62</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="468">
@@ -11655,7 +11655,7 @@
         <v>0</v>
       </c>
       <c r="F468" t="n">
-        <v>59.69</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="469">
@@ -11679,7 +11679,7 @@
         <v>0</v>
       </c>
       <c r="F469" t="n">
-        <v>59.29</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="470">
@@ -11703,7 +11703,7 @@
         <v>1</v>
       </c>
       <c r="F470" t="n">
-        <v>66.26000000000001</v>
+        <v>55.75</v>
       </c>
     </row>
     <row r="471">
@@ -11727,7 +11727,7 @@
         <v>1</v>
       </c>
       <c r="F471" t="n">
-        <v>65.7</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="472">
@@ -11751,7 +11751,7 @@
         <v>1</v>
       </c>
       <c r="F472" t="n">
-        <v>67.06</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="473">
@@ -11775,7 +11775,7 @@
         <v>1</v>
       </c>
       <c r="F473" t="n">
-        <v>57.75</v>
+        <v>53.94</v>
       </c>
     </row>
     <row r="474">
@@ -11799,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="F474" t="n">
-        <v>61.81</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="475">
@@ -11823,7 +11823,7 @@
         <v>1</v>
       </c>
       <c r="F475" t="n">
-        <v>67.7</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="476">
@@ -11847,7 +11847,7 @@
         <v>1</v>
       </c>
       <c r="F476" t="n">
-        <v>68.34999999999999</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="477">
@@ -11871,7 +11871,7 @@
         <v>1</v>
       </c>
       <c r="F477" t="n">
-        <v>66.51000000000001</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="478">
@@ -11895,7 +11895,7 @@
         <v>1</v>
       </c>
       <c r="F478" t="n">
-        <v>64.95999999999999</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="479">
@@ -11919,7 +11919,7 @@
         <v>1</v>
       </c>
       <c r="F479" t="n">
-        <v>65.90000000000001</v>
+        <v>55.53</v>
       </c>
     </row>
     <row r="480">
@@ -11943,7 +11943,7 @@
         <v>1</v>
       </c>
       <c r="F480" t="n">
-        <v>66</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="481">
@@ -11967,7 +11967,7 @@
         <v>1</v>
       </c>
       <c r="F481" t="n">
-        <v>62.13</v>
+        <v>61.56</v>
       </c>
     </row>
     <row r="482">
@@ -11991,7 +11991,7 @@
         <v>0</v>
       </c>
       <c r="F482" t="n">
-        <v>53.96</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="483">
@@ -12015,7 +12015,7 @@
         <v>0</v>
       </c>
       <c r="F483" t="n">
-        <v>54.28</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="484">
@@ -12039,7 +12039,7 @@
         <v>0</v>
       </c>
       <c r="F484" t="n">
-        <v>50.33</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="485">
@@ -12063,7 +12063,7 @@
         <v>0</v>
       </c>
       <c r="F485" t="n">
-        <v>53.26</v>
+        <v>48.77</v>
       </c>
     </row>
     <row r="486">
@@ -12087,7 +12087,7 @@
         <v>0</v>
       </c>
       <c r="F486" t="n">
-        <v>54.33</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="487">
@@ -12111,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="F487" t="n">
-        <v>51.84</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="488">
@@ -12135,7 +12135,7 @@
         <v>0</v>
       </c>
       <c r="F488" t="n">
-        <v>55.2</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="489">
@@ -12159,7 +12159,7 @@
         <v>0</v>
       </c>
       <c r="F489" t="n">
-        <v>50.76</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="490">
@@ -12183,7 +12183,7 @@
         <v>0</v>
       </c>
       <c r="F490" t="n">
-        <v>53.42</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="491">
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="F491" t="n">
-        <v>54.35</v>
+        <v>46.03</v>
       </c>
     </row>
     <row r="492">
@@ -12231,7 +12231,7 @@
         <v>0</v>
       </c>
       <c r="F492" t="n">
-        <v>51.56</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="493">
@@ -12255,7 +12255,7 @@
         <v>0</v>
       </c>
       <c r="F493" t="n">
-        <v>51.29</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="494">
@@ -12279,7 +12279,7 @@
         <v>1</v>
       </c>
       <c r="F494" t="n">
-        <v>51.71</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="495">
@@ -12303,7 +12303,7 @@
         <v>1</v>
       </c>
       <c r="F495" t="n">
-        <v>52.69</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="496">
@@ -12327,7 +12327,7 @@
         <v>1</v>
       </c>
       <c r="F496" t="n">
-        <v>55.66</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="497">
@@ -12351,7 +12351,7 @@
         <v>1</v>
       </c>
       <c r="F497" t="n">
-        <v>53.34</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="498">
@@ -12375,7 +12375,7 @@
         <v>1</v>
       </c>
       <c r="F498" t="n">
-        <v>53.87</v>
+        <v>51.23</v>
       </c>
     </row>
     <row r="499">
@@ -12399,7 +12399,7 @@
         <v>1</v>
       </c>
       <c r="F499" t="n">
-        <v>52.75</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="500">
@@ -12423,7 +12423,7 @@
         <v>1</v>
       </c>
       <c r="F500" t="n">
-        <v>54.42</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="501">
@@ -12447,7 +12447,7 @@
         <v>1</v>
       </c>
       <c r="F501" t="n">
-        <v>58.05</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="502">
@@ -12471,7 +12471,7 @@
         <v>1</v>
       </c>
       <c r="F502" t="n">
-        <v>52.23</v>
+        <v>54.64</v>
       </c>
     </row>
     <row r="503">
@@ -12495,7 +12495,7 @@
         <v>1</v>
       </c>
       <c r="F503" t="n">
-        <v>54.97</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="504">
@@ -12519,7 +12519,7 @@
         <v>1</v>
       </c>
       <c r="F504" t="n">
-        <v>56.35</v>
+        <v>52.01</v>
       </c>
     </row>
     <row r="505">
@@ -12543,7 +12543,7 @@
         <v>1</v>
       </c>
       <c r="F505" t="n">
-        <v>54.19</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="506">
@@ -12567,7 +12567,7 @@
         <v>0</v>
       </c>
       <c r="F506" t="n">
-        <v>51.25</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="507">
@@ -12591,7 +12591,7 @@
         <v>0</v>
       </c>
       <c r="F507" t="n">
-        <v>50.71</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="508">
@@ -12615,7 +12615,7 @@
         <v>0</v>
       </c>
       <c r="F508" t="n">
-        <v>51.63</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="509">
@@ -12639,7 +12639,7 @@
         <v>0</v>
       </c>
       <c r="F509" t="n">
-        <v>48.72</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="510">
@@ -12663,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="F510" t="n">
-        <v>50.95</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="511">
@@ -12687,7 +12687,7 @@
         <v>0</v>
       </c>
       <c r="F511" t="n">
-        <v>50.19</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="512">
@@ -12711,7 +12711,7 @@
         <v>0</v>
       </c>
       <c r="F512" t="n">
-        <v>51.82</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="513">
@@ -12735,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="F513" t="n">
-        <v>53.64</v>
+        <v>54.82</v>
       </c>
     </row>
     <row r="514">
@@ -12759,7 +12759,7 @@
         <v>0</v>
       </c>
       <c r="F514" t="n">
-        <v>55.42</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="515">
@@ -12783,7 +12783,7 @@
         <v>0</v>
       </c>
       <c r="F515" t="n">
-        <v>51.9</v>
+        <v>52.89</v>
       </c>
     </row>
     <row r="516">
@@ -12807,7 +12807,7 @@
         <v>0</v>
       </c>
       <c r="F516" t="n">
-        <v>49.3</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="517">
@@ -12831,7 +12831,7 @@
         <v>0</v>
       </c>
       <c r="F517" t="n">
-        <v>52.84</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="518">
@@ -12855,7 +12855,7 @@
         <v>1</v>
       </c>
       <c r="F518" t="n">
-        <v>51.09</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="519">
@@ -12879,7 +12879,7 @@
         <v>1</v>
       </c>
       <c r="F519" t="n">
-        <v>51.77</v>
+        <v>52.07</v>
       </c>
     </row>
     <row r="520">
@@ -12903,7 +12903,7 @@
         <v>1</v>
       </c>
       <c r="F520" t="n">
-        <v>50.37</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="521">
@@ -12927,7 +12927,7 @@
         <v>1</v>
       </c>
       <c r="F521" t="n">
-        <v>53.47</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="522">
@@ -12951,7 +12951,7 @@
         <v>1</v>
       </c>
       <c r="F522" t="n">
-        <v>55.25</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="523">
@@ -12975,7 +12975,7 @@
         <v>1</v>
       </c>
       <c r="F523" t="n">
-        <v>52.17</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="524">
@@ -12999,7 +12999,7 @@
         <v>1</v>
       </c>
       <c r="F524" t="n">
-        <v>52.27</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="525">
@@ -13023,7 +13023,7 @@
         <v>1</v>
       </c>
       <c r="F525" t="n">
-        <v>50.21</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="526">
@@ -13047,7 +13047,7 @@
         <v>1</v>
       </c>
       <c r="F526" t="n">
-        <v>54.99</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="527">
@@ -13071,7 +13071,7 @@
         <v>1</v>
       </c>
       <c r="F527" t="n">
-        <v>56.57</v>
+        <v>55.18</v>
       </c>
     </row>
     <row r="528">
@@ -13095,7 +13095,7 @@
         <v>1</v>
       </c>
       <c r="F528" t="n">
-        <v>56.38</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="529">
@@ -13119,7 +13119,7 @@
         <v>1</v>
       </c>
       <c r="F529" t="n">
-        <v>54.85</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="530">
@@ -13143,7 +13143,7 @@
         <v>0</v>
       </c>
       <c r="F530" t="n">
-        <v>52.63</v>
+        <v>43.23</v>
       </c>
     </row>
     <row r="531">
@@ -13167,7 +13167,7 @@
         <v>0</v>
       </c>
       <c r="F531" t="n">
-        <v>52.48</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="532">
@@ -13191,7 +13191,7 @@
         <v>0</v>
       </c>
       <c r="F532" t="n">
-        <v>51.19</v>
+        <v>44.06</v>
       </c>
     </row>
     <row r="533">
@@ -13215,7 +13215,7 @@
         <v>0</v>
       </c>
       <c r="F533" t="n">
-        <v>50.59</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="534">
@@ -13239,7 +13239,7 @@
         <v>0</v>
       </c>
       <c r="F534" t="n">
-        <v>51.95</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="535">
@@ -13263,7 +13263,7 @@
         <v>0</v>
       </c>
       <c r="F535" t="n">
-        <v>50.73</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="536">
@@ -13287,7 +13287,7 @@
         <v>0</v>
       </c>
       <c r="F536" t="n">
-        <v>55.85</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="537">
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="F537" t="n">
-        <v>55.03</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="538">
@@ -13335,7 +13335,7 @@
         <v>0</v>
       </c>
       <c r="F538" t="n">
-        <v>49.41</v>
+        <v>48.13</v>
       </c>
     </row>
     <row r="539">
@@ -13359,7 +13359,7 @@
         <v>0</v>
       </c>
       <c r="F539" t="n">
-        <v>55.36</v>
+        <v>50.28</v>
       </c>
     </row>
     <row r="540">
@@ -13383,7 +13383,7 @@
         <v>0</v>
       </c>
       <c r="F540" t="n">
-        <v>52.21</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="541">
@@ -13407,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="F541" t="n">
-        <v>51.55</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="542">
@@ -13431,7 +13431,7 @@
         <v>1</v>
       </c>
       <c r="F542" t="n">
-        <v>51.29</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="543">
@@ -13455,7 +13455,7 @@
         <v>1</v>
       </c>
       <c r="F543" t="n">
-        <v>53.47</v>
+        <v>46.27</v>
       </c>
     </row>
     <row r="544">
@@ -13479,7 +13479,7 @@
         <v>1</v>
       </c>
       <c r="F544" t="n">
-        <v>52.27</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="545">
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="F545" t="n">
-        <v>51.54</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="546">
@@ -13527,7 +13527,7 @@
         <v>1</v>
       </c>
       <c r="F546" t="n">
-        <v>53.7</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="547">
@@ -13551,7 +13551,7 @@
         <v>1</v>
       </c>
       <c r="F547" t="n">
-        <v>55.21</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="548">
@@ -13575,7 +13575,7 @@
         <v>1</v>
       </c>
       <c r="F548" t="n">
-        <v>51.48</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="549">
@@ -13599,7 +13599,7 @@
         <v>1</v>
       </c>
       <c r="F549" t="n">
-        <v>55.35</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="550">
@@ -13623,7 +13623,7 @@
         <v>1</v>
       </c>
       <c r="F550" t="n">
-        <v>51.55</v>
+        <v>48.71</v>
       </c>
     </row>
     <row r="551">
@@ -13647,7 +13647,7 @@
         <v>1</v>
       </c>
       <c r="F551" t="n">
-        <v>50.26</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="552">
@@ -13671,7 +13671,7 @@
         <v>1</v>
       </c>
       <c r="F552" t="n">
-        <v>56.62</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="553">
@@ -13695,7 +13695,7 @@
         <v>1</v>
       </c>
       <c r="F553" t="n">
-        <v>56.57</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="554">
@@ -13719,7 +13719,7 @@
         <v>0</v>
       </c>
       <c r="F554" t="n">
-        <v>51.7</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="555">
@@ -13743,7 +13743,7 @@
         <v>0</v>
       </c>
       <c r="F555" t="n">
-        <v>53.41</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="556">
@@ -13767,7 +13767,7 @@
         <v>0</v>
       </c>
       <c r="F556" t="n">
-        <v>55.55</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="557">
@@ -13791,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="F557" t="n">
-        <v>50.64</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="558">
@@ -13815,7 +13815,7 @@
         <v>0</v>
       </c>
       <c r="F558" t="n">
-        <v>54.96</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="559">
@@ -13839,7 +13839,7 @@
         <v>0</v>
       </c>
       <c r="F559" t="n">
-        <v>52.85</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="560">
@@ -13863,7 +13863,7 @@
         <v>0</v>
       </c>
       <c r="F560" t="n">
-        <v>51.21</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="561">
@@ -13887,7 +13887,7 @@
         <v>0</v>
       </c>
       <c r="F561" t="n">
-        <v>50.2</v>
+        <v>46.71</v>
       </c>
     </row>
     <row r="562">
@@ -13911,7 +13911,7 @@
         <v>0</v>
       </c>
       <c r="F562" t="n">
-        <v>50.37</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="563">
@@ -13935,7 +13935,7 @@
         <v>0</v>
       </c>
       <c r="F563" t="n">
-        <v>54.05</v>
+        <v>47.09</v>
       </c>
     </row>
     <row r="564">
@@ -13959,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="F564" t="n">
-        <v>54.56</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="565">
@@ -13983,7 +13983,7 @@
         <v>0</v>
       </c>
       <c r="F565" t="n">
-        <v>57.87</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="566">
@@ -14007,7 +14007,7 @@
         <v>1</v>
       </c>
       <c r="F566" t="n">
-        <v>57.56</v>
+        <v>46.58</v>
       </c>
     </row>
     <row r="567">
@@ -14031,7 +14031,7 @@
         <v>1</v>
       </c>
       <c r="F567" t="n">
-        <v>57.66</v>
+        <v>46.71</v>
       </c>
     </row>
     <row r="568">
@@ -14055,7 +14055,7 @@
         <v>1</v>
       </c>
       <c r="F568" t="n">
-        <v>53.83</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="569">
@@ -14079,7 +14079,7 @@
         <v>1</v>
       </c>
       <c r="F569" t="n">
-        <v>50.92</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="570">
@@ -14103,7 +14103,7 @@
         <v>1</v>
       </c>
       <c r="F570" t="n">
-        <v>54.83</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="571">
@@ -14127,7 +14127,7 @@
         <v>1</v>
       </c>
       <c r="F571" t="n">
-        <v>54.74</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="572">
@@ -14151,7 +14151,7 @@
         <v>1</v>
       </c>
       <c r="F572" t="n">
-        <v>59.32</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="573">
@@ -14175,7 +14175,7 @@
         <v>1</v>
       </c>
       <c r="F573" t="n">
-        <v>54.64</v>
+        <v>47.29</v>
       </c>
     </row>
     <row r="574">
@@ -14199,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="F574" t="n">
-        <v>55.74</v>
+        <v>46.03</v>
       </c>
     </row>
     <row r="575">
@@ -14223,7 +14223,7 @@
         <v>1</v>
       </c>
       <c r="F575" t="n">
-        <v>56.8</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="576">
@@ -14247,7 +14247,7 @@
         <v>1</v>
       </c>
       <c r="F576" t="n">
-        <v>56.88</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="577">
@@ -14271,7 +14271,7 @@
         <v>1</v>
       </c>
       <c r="F577" t="n">
-        <v>59.28</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="578">
@@ -14295,7 +14295,7 @@
         <v>0</v>
       </c>
       <c r="F578" t="n">
-        <v>51.33</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="579">
@@ -14319,7 +14319,7 @@
         <v>0</v>
       </c>
       <c r="F579" t="n">
-        <v>48.2</v>
+        <v>52.42</v>
       </c>
     </row>
     <row r="580">
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="F580" t="n">
-        <v>48.84</v>
+        <v>54.04</v>
       </c>
     </row>
     <row r="581">
@@ -14367,7 +14367,7 @@
         <v>0</v>
       </c>
       <c r="F581" t="n">
-        <v>46.91</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="582">
@@ -14391,7 +14391,7 @@
         <v>0</v>
       </c>
       <c r="F582" t="n">
-        <v>50.01</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="583">
@@ -14415,7 +14415,7 @@
         <v>0</v>
       </c>
       <c r="F583" t="n">
-        <v>50.62</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="584">
@@ -14439,7 +14439,7 @@
         <v>0</v>
       </c>
       <c r="F584" t="n">
-        <v>49.95</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="585">
@@ -14463,7 +14463,7 @@
         <v>0</v>
       </c>
       <c r="F585" t="n">
-        <v>47.12</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="586">
@@ -14487,7 +14487,7 @@
         <v>0</v>
       </c>
       <c r="F586" t="n">
-        <v>48.95</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="587">
@@ -14511,7 +14511,7 @@
         <v>0</v>
       </c>
       <c r="F587" t="n">
-        <v>47.27</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="588">
@@ -14535,7 +14535,7 @@
         <v>0</v>
       </c>
       <c r="F588" t="n">
-        <v>48.09</v>
+        <v>52.01</v>
       </c>
     </row>
     <row r="589">
@@ -14559,7 +14559,7 @@
         <v>0</v>
       </c>
       <c r="F589" t="n">
-        <v>50.68</v>
+        <v>50.36</v>
       </c>
     </row>
     <row r="590">
@@ -14583,7 +14583,7 @@
         <v>1</v>
       </c>
       <c r="F590" t="n">
-        <v>46.74</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="591">
@@ -14607,7 +14607,7 @@
         <v>1</v>
       </c>
       <c r="F591" t="n">
-        <v>47.16</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="592">
@@ -14631,7 +14631,7 @@
         <v>1</v>
       </c>
       <c r="F592" t="n">
-        <v>49.79</v>
+        <v>51.37</v>
       </c>
     </row>
     <row r="593">
@@ -14655,7 +14655,7 @@
         <v>1</v>
       </c>
       <c r="F593" t="n">
-        <v>49.03</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="594">
@@ -14679,7 +14679,7 @@
         <v>1</v>
       </c>
       <c r="F594" t="n">
-        <v>53.75</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="595">
@@ -14703,7 +14703,7 @@
         <v>1</v>
       </c>
       <c r="F595" t="n">
-        <v>49.63</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="596">
@@ -14727,7 +14727,7 @@
         <v>1</v>
       </c>
       <c r="F596" t="n">
-        <v>51.76</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="597">
@@ -14751,7 +14751,7 @@
         <v>1</v>
       </c>
       <c r="F597" t="n">
-        <v>50.42</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="598">
@@ -14775,7 +14775,7 @@
         <v>1</v>
       </c>
       <c r="F598" t="n">
-        <v>49.06</v>
+        <v>54.02</v>
       </c>
     </row>
     <row r="599">
@@ -14799,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="F599" t="n">
-        <v>57.52</v>
+        <v>51.05</v>
       </c>
     </row>
     <row r="600">
@@ -14823,7 +14823,7 @@
         <v>1</v>
       </c>
       <c r="F600" t="n">
-        <v>52.95</v>
+        <v>52.48</v>
       </c>
     </row>
     <row r="601">
@@ -14847,7 +14847,7 @@
         <v>1</v>
       </c>
       <c r="F601" t="n">
-        <v>53.07</v>
+        <v>54.72</v>
       </c>
     </row>
     <row r="602">
@@ -14871,7 +14871,7 @@
         <v>0</v>
       </c>
       <c r="F602" t="n">
-        <v>53.22</v>
+        <v>52.73</v>
       </c>
     </row>
     <row r="603">
@@ -14895,7 +14895,7 @@
         <v>0</v>
       </c>
       <c r="F603" t="n">
-        <v>54.8</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="604">
@@ -14919,7 +14919,7 @@
         <v>0</v>
       </c>
       <c r="F604" t="n">
-        <v>48.48</v>
+        <v>50.95</v>
       </c>
     </row>
     <row r="605">
@@ -14943,7 +14943,7 @@
         <v>0</v>
       </c>
       <c r="F605" t="n">
-        <v>50.28</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="606">
@@ -14967,7 +14967,7 @@
         <v>0</v>
       </c>
       <c r="F606" t="n">
-        <v>55.78</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="607">
@@ -14991,7 +14991,7 @@
         <v>0</v>
       </c>
       <c r="F607" t="n">
-        <v>50.43</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="608">
@@ -15015,7 +15015,7 @@
         <v>0</v>
       </c>
       <c r="F608" t="n">
-        <v>53.81</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="609">
@@ -15039,7 +15039,7 @@
         <v>0</v>
       </c>
       <c r="F609" t="n">
-        <v>48.84</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="610">
@@ -15063,7 +15063,7 @@
         <v>0</v>
       </c>
       <c r="F610" t="n">
-        <v>52.02</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="611">
@@ -15087,7 +15087,7 @@
         <v>0</v>
       </c>
       <c r="F611" t="n">
-        <v>53.1</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="612">
@@ -15111,7 +15111,7 @@
         <v>0</v>
       </c>
       <c r="F612" t="n">
-        <v>52.02</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="613">
@@ -15135,7 +15135,7 @@
         <v>0</v>
       </c>
       <c r="F613" t="n">
-        <v>50.01</v>
+        <v>53.12</v>
       </c>
     </row>
     <row r="614">
@@ -15159,7 +15159,7 @@
         <v>1</v>
       </c>
       <c r="F614" t="n">
-        <v>57.07</v>
+        <v>52.66</v>
       </c>
     </row>
     <row r="615">
@@ -15183,7 +15183,7 @@
         <v>1</v>
       </c>
       <c r="F615" t="n">
-        <v>53.83</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="616">
@@ -15207,7 +15207,7 @@
         <v>1</v>
       </c>
       <c r="F616" t="n">
-        <v>56.05</v>
+        <v>51.07</v>
       </c>
     </row>
     <row r="617">
@@ -15231,7 +15231,7 @@
         <v>1</v>
       </c>
       <c r="F617" t="n">
-        <v>48.82</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="618">
@@ -15255,7 +15255,7 @@
         <v>1</v>
       </c>
       <c r="F618" t="n">
-        <v>53.15</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="619">
@@ -15279,7 +15279,7 @@
         <v>1</v>
       </c>
       <c r="F619" t="n">
-        <v>55.56</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="620">
@@ -15303,7 +15303,7 @@
         <v>1</v>
       </c>
       <c r="F620" t="n">
-        <v>50.55</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="621">
@@ -15327,7 +15327,7 @@
         <v>1</v>
       </c>
       <c r="F621" t="n">
-        <v>52.76</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="622">
@@ -15351,7 +15351,7 @@
         <v>1</v>
       </c>
       <c r="F622" t="n">
-        <v>52.44</v>
+        <v>51.32</v>
       </c>
     </row>
     <row r="623">
@@ -15375,7 +15375,7 @@
         <v>1</v>
       </c>
       <c r="F623" t="n">
-        <v>54.16</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="624">
@@ -15399,7 +15399,7 @@
         <v>1</v>
       </c>
       <c r="F624" t="n">
-        <v>54.4</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="625">
@@ -15423,7 +15423,7 @@
         <v>1</v>
       </c>
       <c r="F625" t="n">
-        <v>55.99</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="626">
@@ -15447,7 +15447,7 @@
         <v>0</v>
       </c>
       <c r="F626" t="n">
-        <v>47.06</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="627">
@@ -15471,7 +15471,7 @@
         <v>0</v>
       </c>
       <c r="F627" t="n">
-        <v>49.23</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="628">
@@ -15495,7 +15495,7 @@
         <v>0</v>
       </c>
       <c r="F628" t="n">
-        <v>41.44</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="629">
@@ -15519,7 +15519,7 @@
         <v>0</v>
       </c>
       <c r="F629" t="n">
-        <v>45.48</v>
+        <v>50.52</v>
       </c>
     </row>
     <row r="630">
@@ -15543,7 +15543,7 @@
         <v>0</v>
       </c>
       <c r="F630" t="n">
-        <v>47.44</v>
+        <v>52.48</v>
       </c>
     </row>
     <row r="631">
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="F631" t="n">
-        <v>47.27</v>
+        <v>51.07</v>
       </c>
     </row>
     <row r="632">
@@ -15591,7 +15591,7 @@
         <v>0</v>
       </c>
       <c r="F632" t="n">
-        <v>50.29</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="633">
@@ -15615,7 +15615,7 @@
         <v>0</v>
       </c>
       <c r="F633" t="n">
-        <v>45.71</v>
+        <v>48.15</v>
       </c>
     </row>
     <row r="634">
@@ -15639,7 +15639,7 @@
         <v>0</v>
       </c>
       <c r="F634" t="n">
-        <v>50.64</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="635">
@@ -15663,7 +15663,7 @@
         <v>0</v>
       </c>
       <c r="F635" t="n">
-        <v>47.54</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="636">
@@ -15687,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="F636" t="n">
-        <v>50.36</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="637">
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="F637" t="n">
-        <v>43.84</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="638">
@@ -15735,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="F638" t="n">
-        <v>50.06</v>
+        <v>54.27</v>
       </c>
     </row>
     <row r="639">
@@ -15759,7 +15759,7 @@
         <v>1</v>
       </c>
       <c r="F639" t="n">
-        <v>49.07</v>
+        <v>55.06</v>
       </c>
     </row>
     <row r="640">
@@ -15783,7 +15783,7 @@
         <v>1</v>
       </c>
       <c r="F640" t="n">
-        <v>49.38</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="641">
@@ -15807,7 +15807,7 @@
         <v>1</v>
       </c>
       <c r="F641" t="n">
-        <v>49.87</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="642">
@@ -15831,7 +15831,7 @@
         <v>1</v>
       </c>
       <c r="F642" t="n">
-        <v>50.75</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="643">
@@ -15855,7 +15855,7 @@
         <v>1</v>
       </c>
       <c r="F643" t="n">
-        <v>49.63</v>
+        <v>54.73</v>
       </c>
     </row>
     <row r="644">
@@ -15879,7 +15879,7 @@
         <v>1</v>
       </c>
       <c r="F644" t="n">
-        <v>52.14</v>
+        <v>53.23</v>
       </c>
     </row>
     <row r="645">
@@ -15903,7 +15903,7 @@
         <v>1</v>
       </c>
       <c r="F645" t="n">
-        <v>49.3</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="646">
@@ -15927,7 +15927,7 @@
         <v>1</v>
       </c>
       <c r="F646" t="n">
-        <v>51.3</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="647">
@@ -15951,7 +15951,7 @@
         <v>1</v>
       </c>
       <c r="F647" t="n">
-        <v>49.99</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="648">
@@ -15975,7 +15975,7 @@
         <v>1</v>
       </c>
       <c r="F648" t="n">
-        <v>53.62</v>
+        <v>55.89</v>
       </c>
     </row>
     <row r="649">
@@ -15999,7 +15999,7 @@
         <v>1</v>
       </c>
       <c r="F649" t="n">
-        <v>54.07</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="650">
@@ -16023,7 +16023,7 @@
         <v>0</v>
       </c>
       <c r="F650" t="n">
-        <v>42.84</v>
+        <v>52.11</v>
       </c>
     </row>
     <row r="651">
@@ -16047,7 +16047,7 @@
         <v>0</v>
       </c>
       <c r="F651" t="n">
-        <v>41.48</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="652">
@@ -16071,7 +16071,7 @@
         <v>0</v>
       </c>
       <c r="F652" t="n">
-        <v>46.72</v>
+        <v>50.14</v>
       </c>
     </row>
     <row r="653">
@@ -16095,7 +16095,7 @@
         <v>0</v>
       </c>
       <c r="F653" t="n">
-        <v>43.07</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="654">
@@ -16119,7 +16119,7 @@
         <v>0</v>
       </c>
       <c r="F654" t="n">
-        <v>45.48</v>
+        <v>50.42</v>
       </c>
     </row>
     <row r="655">
@@ -16143,7 +16143,7 @@
         <v>0</v>
       </c>
       <c r="F655" t="n">
-        <v>48.96</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="656">
@@ -16167,7 +16167,7 @@
         <v>0</v>
       </c>
       <c r="F656" t="n">
-        <v>47.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="657">
@@ -16191,7 +16191,7 @@
         <v>0</v>
       </c>
       <c r="F657" t="n">
-        <v>42.87</v>
+        <v>50.99</v>
       </c>
     </row>
     <row r="658">
@@ -16215,7 +16215,7 @@
         <v>0</v>
       </c>
       <c r="F658" t="n">
-        <v>51.04</v>
+        <v>53.73</v>
       </c>
     </row>
     <row r="659">
@@ -16239,7 +16239,7 @@
         <v>0</v>
       </c>
       <c r="F659" t="n">
-        <v>49.12</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="660">
@@ -16263,7 +16263,7 @@
         <v>0</v>
       </c>
       <c r="F660" t="n">
-        <v>48.87</v>
+        <v>53.37</v>
       </c>
     </row>
     <row r="661">
@@ -16287,7 +16287,7 @@
         <v>0</v>
       </c>
       <c r="F661" t="n">
-        <v>47.35</v>
+        <v>57.84</v>
       </c>
     </row>
     <row r="662">
@@ -16311,7 +16311,7 @@
         <v>1</v>
       </c>
       <c r="F662" t="n">
-        <v>45.74</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="663">
@@ -16335,7 +16335,7 @@
         <v>1</v>
       </c>
       <c r="F663" t="n">
-        <v>49.78</v>
+        <v>55.79</v>
       </c>
     </row>
     <row r="664">
@@ -16359,7 +16359,7 @@
         <v>1</v>
       </c>
       <c r="F664" t="n">
-        <v>51.71</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="665">
@@ -16383,7 +16383,7 @@
         <v>1</v>
       </c>
       <c r="F665" t="n">
-        <v>49.36</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="666">
@@ -16407,7 +16407,7 @@
         <v>1</v>
       </c>
       <c r="F666" t="n">
-        <v>47.54</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="667">
@@ -16431,7 +16431,7 @@
         <v>1</v>
       </c>
       <c r="F667" t="n">
-        <v>52.58</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="668">
@@ -16455,7 +16455,7 @@
         <v>1</v>
       </c>
       <c r="F668" t="n">
-        <v>50.72</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="669">
@@ -16479,7 +16479,7 @@
         <v>1</v>
       </c>
       <c r="F669" t="n">
-        <v>54.5</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="670">
@@ -16503,7 +16503,7 @@
         <v>1</v>
       </c>
       <c r="F670" t="n">
-        <v>51.08</v>
+        <v>52</v>
       </c>
     </row>
     <row r="671">
@@ -16527,7 +16527,7 @@
         <v>1</v>
       </c>
       <c r="F671" t="n">
-        <v>51.42</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="672">
@@ -16551,7 +16551,7 @@
         <v>1</v>
       </c>
       <c r="F672" t="n">
-        <v>52.59</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="673">
@@ -16575,7 +16575,7 @@
         <v>1</v>
       </c>
       <c r="F673" t="n">
-        <v>50.09</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="674">
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="F674" t="n">
-        <v>54.13</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="675">
@@ -16623,7 +16623,7 @@
         <v>0</v>
       </c>
       <c r="F675" t="n">
-        <v>52.58</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="676">
@@ -16647,7 +16647,7 @@
         <v>0</v>
       </c>
       <c r="F676" t="n">
-        <v>56.02</v>
+        <v>55.11</v>
       </c>
     </row>
     <row r="677">
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="F677" t="n">
-        <v>56.84</v>
+        <v>52.92</v>
       </c>
     </row>
     <row r="678">
@@ -16695,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="F678" t="n">
-        <v>55.86</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="679">
@@ -16719,7 +16719,7 @@
         <v>0</v>
       </c>
       <c r="F679" t="n">
-        <v>55.39</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="680">
@@ -16743,7 +16743,7 @@
         <v>0</v>
       </c>
       <c r="F680" t="n">
-        <v>54.65</v>
+        <v>54.49</v>
       </c>
     </row>
     <row r="681">
@@ -16767,7 +16767,7 @@
         <v>0</v>
       </c>
       <c r="F681" t="n">
-        <v>52.4</v>
+        <v>54.02</v>
       </c>
     </row>
     <row r="682">
@@ -16791,7 +16791,7 @@
         <v>0</v>
       </c>
       <c r="F682" t="n">
-        <v>56.89</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="683">
@@ -16815,7 +16815,7 @@
         <v>0</v>
       </c>
       <c r="F683" t="n">
-        <v>54.41</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="684">
@@ -16839,7 +16839,7 @@
         <v>0</v>
       </c>
       <c r="F684" t="n">
-        <v>55.39</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="685">
@@ -16863,7 +16863,7 @@
         <v>0</v>
       </c>
       <c r="F685" t="n">
-        <v>50.64</v>
+        <v>57.87</v>
       </c>
     </row>
     <row r="686">
@@ -16887,7 +16887,7 @@
         <v>1</v>
       </c>
       <c r="F686" t="n">
-        <v>52.09</v>
+        <v>59.37</v>
       </c>
     </row>
     <row r="687">
@@ -16911,7 +16911,7 @@
         <v>1</v>
       </c>
       <c r="F687" t="n">
-        <v>57.19</v>
+        <v>56.82</v>
       </c>
     </row>
     <row r="688">
@@ -16935,7 +16935,7 @@
         <v>1</v>
       </c>
       <c r="F688" t="n">
-        <v>59.04</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="689">
@@ -16959,7 +16959,7 @@
         <v>1</v>
       </c>
       <c r="F689" t="n">
-        <v>56.85</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="690">
@@ -16983,7 +16983,7 @@
         <v>1</v>
       </c>
       <c r="F690" t="n">
-        <v>54.99</v>
+        <v>61.09</v>
       </c>
     </row>
     <row r="691">
@@ -17007,7 +17007,7 @@
         <v>1</v>
       </c>
       <c r="F691" t="n">
-        <v>60.93</v>
+        <v>62.94</v>
       </c>
     </row>
     <row r="692">
@@ -17031,7 +17031,7 @@
         <v>1</v>
       </c>
       <c r="F692" t="n">
-        <v>58.5</v>
+        <v>58.63</v>
       </c>
     </row>
     <row r="693">
@@ -17055,7 +17055,7 @@
         <v>1</v>
       </c>
       <c r="F693" t="n">
-        <v>59.5</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="694">
@@ -17079,7 +17079,7 @@
         <v>1</v>
       </c>
       <c r="F694" t="n">
-        <v>59.32</v>
+        <v>58.62</v>
       </c>
     </row>
     <row r="695">
@@ -17103,7 +17103,7 @@
         <v>1</v>
       </c>
       <c r="F695" t="n">
-        <v>56.59</v>
+        <v>57.83</v>
       </c>
     </row>
     <row r="696">
@@ -17127,7 +17127,7 @@
         <v>1</v>
       </c>
       <c r="F696" t="n">
-        <v>57.35</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="697">
@@ -17151,7 +17151,7 @@
         <v>1</v>
       </c>
       <c r="F697" t="n">
-        <v>60.85</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="698">
@@ -17175,7 +17175,7 @@
         <v>0</v>
       </c>
       <c r="F698" t="n">
-        <v>49.51</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="699">
@@ -17199,7 +17199,7 @@
         <v>0</v>
       </c>
       <c r="F699" t="n">
-        <v>46.2</v>
+        <v>39.77</v>
       </c>
     </row>
     <row r="700">
@@ -17223,7 +17223,7 @@
         <v>0</v>
       </c>
       <c r="F700" t="n">
-        <v>48.73</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="701">
@@ -17247,7 +17247,7 @@
         <v>0</v>
       </c>
       <c r="F701" t="n">
-        <v>47.49</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="702">
@@ -17271,7 +17271,7 @@
         <v>0</v>
       </c>
       <c r="F702" t="n">
-        <v>50.87</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="703">
@@ -17295,7 +17295,7 @@
         <v>0</v>
       </c>
       <c r="F703" t="n">
-        <v>49.8</v>
+        <v>47.47</v>
       </c>
     </row>
     <row r="704">
@@ -17319,7 +17319,7 @@
         <v>0</v>
       </c>
       <c r="F704" t="n">
-        <v>50.27</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="705">
@@ -17343,7 +17343,7 @@
         <v>0</v>
       </c>
       <c r="F705" t="n">
-        <v>47.06</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="706">
@@ -17367,7 +17367,7 @@
         <v>0</v>
       </c>
       <c r="F706" t="n">
-        <v>51.59</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="707">
@@ -17391,7 +17391,7 @@
         <v>0</v>
       </c>
       <c r="F707" t="n">
-        <v>48.99</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="708">
@@ -17415,7 +17415,7 @@
         <v>0</v>
       </c>
       <c r="F708" t="n">
-        <v>48.03</v>
+        <v>41.33</v>
       </c>
     </row>
     <row r="709">
@@ -17439,7 +17439,7 @@
         <v>0</v>
       </c>
       <c r="F709" t="n">
-        <v>49.93</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="710">
@@ -17463,7 +17463,7 @@
         <v>1</v>
       </c>
       <c r="F710" t="n">
-        <v>51.85</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="711">
@@ -17487,7 +17487,7 @@
         <v>1</v>
       </c>
       <c r="F711" t="n">
-        <v>52.42</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="712">
@@ -17511,7 +17511,7 @@
         <v>1</v>
       </c>
       <c r="F712" t="n">
-        <v>49.07</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="713">
@@ -17535,7 +17535,7 @@
         <v>1</v>
       </c>
       <c r="F713" t="n">
-        <v>50.19</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="714">
@@ -17559,7 +17559,7 @@
         <v>1</v>
       </c>
       <c r="F714" t="n">
-        <v>51.43</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="715">
@@ -17583,7 +17583,7 @@
         <v>1</v>
       </c>
       <c r="F715" t="n">
-        <v>51.44</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="716">
@@ -17607,7 +17607,7 @@
         <v>1</v>
       </c>
       <c r="F716" t="n">
-        <v>52.42</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="717">
@@ -17631,7 +17631,7 @@
         <v>1</v>
       </c>
       <c r="F717" t="n">
-        <v>56.39</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="718">
@@ -17655,7 +17655,7 @@
         <v>1</v>
       </c>
       <c r="F718" t="n">
-        <v>50.27</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="719">
@@ -17679,7 +17679,7 @@
         <v>1</v>
       </c>
       <c r="F719" t="n">
-        <v>51.25</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="720">
@@ -17703,7 +17703,7 @@
         <v>1</v>
       </c>
       <c r="F720" t="n">
-        <v>50.54</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="721">
@@ -17727,7 +17727,7 @@
         <v>1</v>
       </c>
       <c r="F721" t="n">
-        <v>51.42</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="722">
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="F722" t="n">
-        <v>52.28</v>
+        <v>47.99</v>
       </c>
     </row>
     <row r="723">
@@ -17775,7 +17775,7 @@
         <v>0</v>
       </c>
       <c r="F723" t="n">
-        <v>49.5</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="724">
@@ -17799,7 +17799,7 @@
         <v>0</v>
       </c>
       <c r="F724" t="n">
-        <v>54.66</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="725">
@@ -17823,7 +17823,7 @@
         <v>0</v>
       </c>
       <c r="F725" t="n">
-        <v>52.94</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="726">
@@ -17847,7 +17847,7 @@
         <v>0</v>
       </c>
       <c r="F726" t="n">
-        <v>57.15</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="727">
@@ -17871,7 +17871,7 @@
         <v>0</v>
       </c>
       <c r="F727" t="n">
-        <v>55.14</v>
+        <v>52.49</v>
       </c>
     </row>
     <row r="728">
@@ -17895,7 +17895,7 @@
         <v>0</v>
       </c>
       <c r="F728" t="n">
-        <v>52.74</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="729">
@@ -17919,7 +17919,7 @@
         <v>0</v>
       </c>
       <c r="F729" t="n">
-        <v>51.1</v>
+        <v>55.06</v>
       </c>
     </row>
     <row r="730">
@@ -17943,7 +17943,7 @@
         <v>0</v>
       </c>
       <c r="F730" t="n">
-        <v>51.48</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="731">
@@ -17967,7 +17967,7 @@
         <v>0</v>
       </c>
       <c r="F731" t="n">
-        <v>53.79</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="732">
@@ -17991,7 +17991,7 @@
         <v>0</v>
       </c>
       <c r="F732" t="n">
-        <v>53.42</v>
+        <v>53.41</v>
       </c>
     </row>
     <row r="733">
@@ -18015,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="F733" t="n">
-        <v>59.24</v>
+        <v>51.49</v>
       </c>
     </row>
     <row r="734">
@@ -18039,7 +18039,7 @@
         <v>1</v>
       </c>
       <c r="F734" t="n">
-        <v>53.19</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="735">
@@ -18063,7 +18063,7 @@
         <v>1</v>
       </c>
       <c r="F735" t="n">
-        <v>56.89</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="736">
@@ -18087,7 +18087,7 @@
         <v>1</v>
       </c>
       <c r="F736" t="n">
-        <v>55.94</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="737">
@@ -18111,7 +18111,7 @@
         <v>1</v>
       </c>
       <c r="F737" t="n">
-        <v>54.46</v>
+        <v>53.02</v>
       </c>
     </row>
     <row r="738">
@@ -18135,7 +18135,7 @@
         <v>1</v>
       </c>
       <c r="F738" t="n">
-        <v>56.72</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="739">
@@ -18159,7 +18159,7 @@
         <v>1</v>
       </c>
       <c r="F739" t="n">
-        <v>53.15</v>
+        <v>55.95</v>
       </c>
     </row>
     <row r="740">
@@ -18183,7 +18183,7 @@
         <v>1</v>
       </c>
       <c r="F740" t="n">
-        <v>56.06</v>
+        <v>56.89</v>
       </c>
     </row>
     <row r="741">
@@ -18207,7 +18207,7 @@
         <v>1</v>
       </c>
       <c r="F741" t="n">
-        <v>55.59</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="742">
@@ -18231,7 +18231,7 @@
         <v>1</v>
       </c>
       <c r="F742" t="n">
-        <v>52.36</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="743">
@@ -18255,7 +18255,7 @@
         <v>1</v>
       </c>
       <c r="F743" t="n">
-        <v>57.03</v>
+        <v>56.85</v>
       </c>
     </row>
     <row r="744">
@@ -18279,7 +18279,7 @@
         <v>1</v>
       </c>
       <c r="F744" t="n">
-        <v>57.85</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="745">
@@ -18303,7 +18303,7 @@
         <v>1</v>
       </c>
       <c r="F745" t="n">
-        <v>54.16</v>
+        <v>55.32</v>
       </c>
     </row>
     <row r="746">
@@ -18327,7 +18327,7 @@
         <v>0</v>
       </c>
       <c r="F746" t="n">
-        <v>52.54</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="747">
@@ -18351,7 +18351,7 @@
         <v>0</v>
       </c>
       <c r="F747" t="n">
-        <v>51.68</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="748">
@@ -18375,7 +18375,7 @@
         <v>0</v>
       </c>
       <c r="F748" t="n">
-        <v>52.22</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="749">
@@ -18399,7 +18399,7 @@
         <v>0</v>
       </c>
       <c r="F749" t="n">
-        <v>52.93</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="750">
@@ -18423,7 +18423,7 @@
         <v>0</v>
       </c>
       <c r="F750" t="n">
-        <v>50.09</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="751">
@@ -18447,7 +18447,7 @@
         <v>0</v>
       </c>
       <c r="F751" t="n">
-        <v>51.51</v>
+        <v>51.01</v>
       </c>
     </row>
     <row r="752">
@@ -18471,7 +18471,7 @@
         <v>0</v>
       </c>
       <c r="F752" t="n">
-        <v>51.59</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="753">
@@ -18495,7 +18495,7 @@
         <v>0</v>
       </c>
       <c r="F753" t="n">
-        <v>46.41</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="754">
@@ -18519,7 +18519,7 @@
         <v>0</v>
       </c>
       <c r="F754" t="n">
-        <v>55.04</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="755">
@@ -18543,7 +18543,7 @@
         <v>0</v>
       </c>
       <c r="F755" t="n">
-        <v>51.67</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="756">
@@ -18567,7 +18567,7 @@
         <v>0</v>
       </c>
       <c r="F756" t="n">
-        <v>52.91</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="757">
@@ -18591,7 +18591,7 @@
         <v>0</v>
       </c>
       <c r="F757" t="n">
-        <v>48.27</v>
+        <v>50.17</v>
       </c>
     </row>
     <row r="758">
@@ -18615,7 +18615,7 @@
         <v>1</v>
       </c>
       <c r="F758" t="n">
-        <v>51.2</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="759">
@@ -18639,7 +18639,7 @@
         <v>1</v>
       </c>
       <c r="F759" t="n">
-        <v>55.2</v>
+        <v>46.34</v>
       </c>
     </row>
     <row r="760">
@@ -18663,7 +18663,7 @@
         <v>1</v>
       </c>
       <c r="F760" t="n">
-        <v>54.74</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="761">
@@ -18687,7 +18687,7 @@
         <v>1</v>
       </c>
       <c r="F761" t="n">
-        <v>53.01</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="762">
@@ -18711,7 +18711,7 @@
         <v>1</v>
       </c>
       <c r="F762" t="n">
-        <v>53.96</v>
+        <v>49.38</v>
       </c>
     </row>
     <row r="763">
@@ -18735,7 +18735,7 @@
         <v>1</v>
       </c>
       <c r="F763" t="n">
-        <v>54.54</v>
+        <v>48.43</v>
       </c>
     </row>
     <row r="764">
@@ -18759,7 +18759,7 @@
         <v>1</v>
       </c>
       <c r="F764" t="n">
-        <v>58.13</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="765">
@@ -18783,7 +18783,7 @@
         <v>1</v>
       </c>
       <c r="F765" t="n">
-        <v>53.32</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="766">
@@ -18807,7 +18807,7 @@
         <v>1</v>
       </c>
       <c r="F766" t="n">
-        <v>59.44</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="767">
@@ -18831,7 +18831,7 @@
         <v>1</v>
       </c>
       <c r="F767" t="n">
-        <v>52.24</v>
+        <v>49.61</v>
       </c>
     </row>
     <row r="768">
@@ -18855,7 +18855,7 @@
         <v>1</v>
       </c>
       <c r="F768" t="n">
-        <v>55.2</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="769">
@@ -18879,7 +18879,7 @@
         <v>1</v>
       </c>
       <c r="F769" t="n">
-        <v>55.54</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="770">
@@ -18903,7 +18903,7 @@
         <v>0</v>
       </c>
       <c r="F770" t="n">
-        <v>55.37</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="771">
@@ -18927,7 +18927,7 @@
         <v>0</v>
       </c>
       <c r="F771" t="n">
-        <v>56.22</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="772">
@@ -18951,7 +18951,7 @@
         <v>0</v>
       </c>
       <c r="F772" t="n">
-        <v>59.55</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="773">
@@ -18975,7 +18975,7 @@
         <v>0</v>
       </c>
       <c r="F773" t="n">
-        <v>53.57</v>
+        <v>57.04</v>
       </c>
     </row>
     <row r="774">
@@ -18999,7 +18999,7 @@
         <v>0</v>
       </c>
       <c r="F774" t="n">
-        <v>53.89</v>
+        <v>58.94</v>
       </c>
     </row>
     <row r="775">
@@ -19023,7 +19023,7 @@
         <v>0</v>
       </c>
       <c r="F775" t="n">
-        <v>55.52</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="776">
@@ -19047,7 +19047,7 @@
         <v>0</v>
       </c>
       <c r="F776" t="n">
-        <v>52.74</v>
+        <v>52.26</v>
       </c>
     </row>
     <row r="777">
@@ -19071,7 +19071,7 @@
         <v>0</v>
       </c>
       <c r="F777" t="n">
-        <v>55.46</v>
+        <v>55.62</v>
       </c>
     </row>
     <row r="778">
@@ -19095,7 +19095,7 @@
         <v>0</v>
       </c>
       <c r="F778" t="n">
-        <v>52.76</v>
+        <v>51.31</v>
       </c>
     </row>
     <row r="779">
@@ -19119,7 +19119,7 @@
         <v>0</v>
       </c>
       <c r="F779" t="n">
-        <v>58.14</v>
+        <v>54.64</v>
       </c>
     </row>
     <row r="780">
@@ -19143,7 +19143,7 @@
         <v>0</v>
       </c>
       <c r="F780" t="n">
-        <v>55.65</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="781">
@@ -19167,7 +19167,7 @@
         <v>0</v>
       </c>
       <c r="F781" t="n">
-        <v>56.29</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="782">
@@ -19191,7 +19191,7 @@
         <v>1</v>
       </c>
       <c r="F782" t="n">
-        <v>55.75</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="783">
@@ -19215,7 +19215,7 @@
         <v>1</v>
       </c>
       <c r="F783" t="n">
-        <v>57.9</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="784">
@@ -19239,7 +19239,7 @@
         <v>1</v>
       </c>
       <c r="F784" t="n">
-        <v>55.38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="785">
@@ -19263,7 +19263,7 @@
         <v>1</v>
       </c>
       <c r="F785" t="n">
-        <v>59.72</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="786">
@@ -19287,7 +19287,7 @@
         <v>1</v>
       </c>
       <c r="F786" t="n">
-        <v>57.31</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="787">
@@ -19311,7 +19311,7 @@
         <v>1</v>
       </c>
       <c r="F787" t="n">
-        <v>57.14</v>
+        <v>51.44</v>
       </c>
     </row>
     <row r="788">
@@ -19335,7 +19335,7 @@
         <v>1</v>
       </c>
       <c r="F788" t="n">
-        <v>56.57</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="789">
@@ -19359,7 +19359,7 @@
         <v>1</v>
       </c>
       <c r="F789" t="n">
-        <v>56.92</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="790">
@@ -19383,7 +19383,7 @@
         <v>1</v>
       </c>
       <c r="F790" t="n">
-        <v>57.62</v>
+        <v>48.14</v>
       </c>
     </row>
     <row r="791">
@@ -19407,7 +19407,7 @@
         <v>1</v>
       </c>
       <c r="F791" t="n">
-        <v>59.77</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="792">
@@ -19431,7 +19431,7 @@
         <v>1</v>
       </c>
       <c r="F792" t="n">
-        <v>58.92</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="793">
@@ -19455,7 +19455,7 @@
         <v>1</v>
       </c>
       <c r="F793" t="n">
-        <v>58.01</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="794">
@@ -19479,7 +19479,7 @@
         <v>0</v>
       </c>
       <c r="F794" t="n">
-        <v>51.35</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="795">
@@ -19503,7 +19503,7 @@
         <v>0</v>
       </c>
       <c r="F795" t="n">
-        <v>52.5</v>
+        <v>49.79</v>
       </c>
     </row>
     <row r="796">
@@ -19527,7 +19527,7 @@
         <v>0</v>
       </c>
       <c r="F796" t="n">
-        <v>53.44</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="797">
@@ -19551,7 +19551,7 @@
         <v>0</v>
       </c>
       <c r="F797" t="n">
-        <v>51.34</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="798">
@@ -19575,7 +19575,7 @@
         <v>0</v>
       </c>
       <c r="F798" t="n">
-        <v>52.97</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="799">
@@ -19599,7 +19599,7 @@
         <v>0</v>
       </c>
       <c r="F799" t="n">
-        <v>55.22</v>
+        <v>54.49</v>
       </c>
     </row>
     <row r="800">
@@ -19623,7 +19623,7 @@
         <v>0</v>
       </c>
       <c r="F800" t="n">
-        <v>53.28</v>
+        <v>56.08</v>
       </c>
     </row>
     <row r="801">
@@ -19647,7 +19647,7 @@
         <v>0</v>
       </c>
       <c r="F801" t="n">
-        <v>52.94</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="802">
@@ -19671,7 +19671,7 @@
         <v>0</v>
       </c>
       <c r="F802" t="n">
-        <v>57.66</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="803">
@@ -19695,7 +19695,7 @@
         <v>0</v>
       </c>
       <c r="F803" t="n">
-        <v>54.01</v>
+        <v>56.92</v>
       </c>
     </row>
     <row r="804">
@@ -19719,7 +19719,7 @@
         <v>0</v>
       </c>
       <c r="F804" t="n">
-        <v>53.77</v>
+        <v>59.16</v>
       </c>
     </row>
     <row r="805">
@@ -19743,7 +19743,7 @@
         <v>0</v>
       </c>
       <c r="F805" t="n">
-        <v>54.38</v>
+        <v>58.87</v>
       </c>
     </row>
     <row r="806">
@@ -19767,7 +19767,7 @@
         <v>1</v>
       </c>
       <c r="F806" t="n">
-        <v>54.96</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="807">
@@ -19791,7 +19791,7 @@
         <v>1</v>
       </c>
       <c r="F807" t="n">
-        <v>55.17</v>
+        <v>58</v>
       </c>
     </row>
     <row r="808">
@@ -19815,7 +19815,7 @@
         <v>1</v>
       </c>
       <c r="F808" t="n">
-        <v>54.76</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="809">
@@ -19839,7 +19839,7 @@
         <v>1</v>
       </c>
       <c r="F809" t="n">
-        <v>56.58</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="810">
@@ -19863,7 +19863,7 @@
         <v>1</v>
       </c>
       <c r="F810" t="n">
-        <v>49.57</v>
+        <v>56.51</v>
       </c>
     </row>
     <row r="811">
@@ -19887,7 +19887,7 @@
         <v>1</v>
       </c>
       <c r="F811" t="n">
-        <v>53.51</v>
+        <v>51.37</v>
       </c>
     </row>
     <row r="812">
@@ -19911,7 +19911,7 @@
         <v>1</v>
       </c>
       <c r="F812" t="n">
-        <v>56.98</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="813">
@@ -19935,7 +19935,7 @@
         <v>1</v>
       </c>
       <c r="F813" t="n">
-        <v>56.87</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="814">
@@ -19959,7 +19959,7 @@
         <v>1</v>
       </c>
       <c r="F814" t="n">
-        <v>58.15</v>
+        <v>58.16</v>
       </c>
     </row>
     <row r="815">
@@ -19983,7 +19983,7 @@
         <v>1</v>
       </c>
       <c r="F815" t="n">
-        <v>54.83</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="816">
@@ -20007,7 +20007,7 @@
         <v>1</v>
       </c>
       <c r="F816" t="n">
-        <v>54.28</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="817">
@@ -20031,7 +20031,7 @@
         <v>1</v>
       </c>
       <c r="F817" t="n">
-        <v>55.56</v>
+        <v>57.09</v>
       </c>
     </row>
     <row r="818">
@@ -20055,7 +20055,7 @@
         <v>0</v>
       </c>
       <c r="F818" t="n">
-        <v>48.93</v>
+        <v>48.49</v>
       </c>
     </row>
     <row r="819">
@@ -20079,7 +20079,7 @@
         <v>0</v>
       </c>
       <c r="F819" t="n">
-        <v>48.26</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="820">
@@ -20103,7 +20103,7 @@
         <v>0</v>
       </c>
       <c r="F820" t="n">
-        <v>57.38</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="821">
@@ -20127,7 +20127,7 @@
         <v>0</v>
       </c>
       <c r="F821" t="n">
-        <v>54.07</v>
+        <v>53.18</v>
       </c>
     </row>
     <row r="822">
@@ -20151,7 +20151,7 @@
         <v>0</v>
       </c>
       <c r="F822" t="n">
-        <v>55.38</v>
+        <v>52.66</v>
       </c>
     </row>
     <row r="823">
@@ -20175,7 +20175,7 @@
         <v>0</v>
       </c>
       <c r="F823" t="n">
-        <v>49.51</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="824">
@@ -20199,7 +20199,7 @@
         <v>0</v>
       </c>
       <c r="F824" t="n">
-        <v>49.74</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="825">
@@ -20223,7 +20223,7 @@
         <v>0</v>
       </c>
       <c r="F825" t="n">
-        <v>48.99</v>
+        <v>52.66</v>
       </c>
     </row>
     <row r="826">
@@ -20247,7 +20247,7 @@
         <v>0</v>
       </c>
       <c r="F826" t="n">
-        <v>52.13</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="827">
@@ -20271,7 +20271,7 @@
         <v>0</v>
       </c>
       <c r="F827" t="n">
-        <v>51.12</v>
+        <v>50.13</v>
       </c>
     </row>
     <row r="828">
@@ -20295,7 +20295,7 @@
         <v>0</v>
       </c>
       <c r="F828" t="n">
-        <v>50.26</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="829">
@@ -20319,7 +20319,7 @@
         <v>0</v>
       </c>
       <c r="F829" t="n">
-        <v>52.2</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="830">
@@ -20343,7 +20343,7 @@
         <v>1</v>
       </c>
       <c r="F830" t="n">
-        <v>52.43</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="831">
@@ -20367,7 +20367,7 @@
         <v>1</v>
       </c>
       <c r="F831" t="n">
-        <v>51.52</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="832">
@@ -20391,7 +20391,7 @@
         <v>1</v>
       </c>
       <c r="F832" t="n">
-        <v>51.44</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="833">
@@ -20415,7 +20415,7 @@
         <v>1</v>
       </c>
       <c r="F833" t="n">
-        <v>55.79</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="834">
@@ -20439,7 +20439,7 @@
         <v>1</v>
       </c>
       <c r="F834" t="n">
-        <v>52.31</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="835">
@@ -20463,7 +20463,7 @@
         <v>1</v>
       </c>
       <c r="F835" t="n">
-        <v>55.4</v>
+        <v>53.01</v>
       </c>
     </row>
     <row r="836">
@@ -20487,7 +20487,7 @@
         <v>1</v>
       </c>
       <c r="F836" t="n">
-        <v>54.58</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="837">
@@ -20511,7 +20511,7 @@
         <v>1</v>
       </c>
       <c r="F837" t="n">
-        <v>57.62</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="838">
@@ -20535,7 +20535,7 @@
         <v>1</v>
       </c>
       <c r="F838" t="n">
-        <v>56.53</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="839">
@@ -20559,7 +20559,7 @@
         <v>1</v>
       </c>
       <c r="F839" t="n">
-        <v>51.14</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="840">
@@ -20583,7 +20583,7 @@
         <v>1</v>
       </c>
       <c r="F840" t="n">
-        <v>52.47</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="841">
@@ -20607,7 +20607,7 @@
         <v>1</v>
       </c>
       <c r="F841" t="n">
-        <v>54.44</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="842">
@@ -20631,7 +20631,7 @@
         <v>0</v>
       </c>
       <c r="F842" t="n">
-        <v>50.23</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="843">
@@ -20655,7 +20655,7 @@
         <v>0</v>
       </c>
       <c r="F843" t="n">
-        <v>48.52</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="844">
@@ -20679,7 +20679,7 @@
         <v>0</v>
       </c>
       <c r="F844" t="n">
-        <v>47.98</v>
+        <v>50.34</v>
       </c>
     </row>
     <row r="845">
@@ -20703,7 +20703,7 @@
         <v>0</v>
       </c>
       <c r="F845" t="n">
-        <v>50.23</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="846">
@@ -20727,7 +20727,7 @@
         <v>0</v>
       </c>
       <c r="F846" t="n">
-        <v>50.71</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="847">
@@ -20751,7 +20751,7 @@
         <v>0</v>
       </c>
       <c r="F847" t="n">
-        <v>47.41</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="848">
@@ -20775,7 +20775,7 @@
         <v>0</v>
       </c>
       <c r="F848" t="n">
-        <v>49.52</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="849">
@@ -20799,7 +20799,7 @@
         <v>0</v>
       </c>
       <c r="F849" t="n">
-        <v>47.82</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="850">
@@ -20823,7 +20823,7 @@
         <v>0</v>
       </c>
       <c r="F850" t="n">
-        <v>46.94</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="851">
@@ -20847,7 +20847,7 @@
         <v>0</v>
       </c>
       <c r="F851" t="n">
-        <v>45.72</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="852">
@@ -20871,7 +20871,7 @@
         <v>0</v>
       </c>
       <c r="F852" t="n">
-        <v>47.17</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="853">
@@ -20895,7 +20895,7 @@
         <v>0</v>
       </c>
       <c r="F853" t="n">
-        <v>49.07</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="854">
@@ -20919,7 +20919,7 @@
         <v>1</v>
       </c>
       <c r="F854" t="n">
-        <v>52.16</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="855">
@@ -20943,7 +20943,7 @@
         <v>1</v>
       </c>
       <c r="F855" t="n">
-        <v>50.04</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="856">
@@ -20967,7 +20967,7 @@
         <v>1</v>
       </c>
       <c r="F856" t="n">
-        <v>48.47</v>
+        <v>57.67</v>
       </c>
     </row>
     <row r="857">
@@ -20991,7 +20991,7 @@
         <v>1</v>
       </c>
       <c r="F857" t="n">
-        <v>49.36</v>
+        <v>56.14</v>
       </c>
     </row>
     <row r="858">
@@ -21015,7 +21015,7 @@
         <v>1</v>
       </c>
       <c r="F858" t="n">
-        <v>52.23</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="859">
@@ -21039,7 +21039,7 @@
         <v>1</v>
       </c>
       <c r="F859" t="n">
-        <v>47.2</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="860">
@@ -21063,7 +21063,7 @@
         <v>1</v>
       </c>
       <c r="F860" t="n">
-        <v>53.29</v>
+        <v>52.13</v>
       </c>
     </row>
     <row r="861">
@@ -21087,7 +21087,7 @@
         <v>1</v>
       </c>
       <c r="F861" t="n">
-        <v>52.51</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="862">
@@ -21111,7 +21111,7 @@
         <v>1</v>
       </c>
       <c r="F862" t="n">
-        <v>52.36</v>
+        <v>52.16</v>
       </c>
     </row>
     <row r="863">
@@ -21135,7 +21135,7 @@
         <v>1</v>
       </c>
       <c r="F863" t="n">
-        <v>53.62</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="864">
@@ -21159,7 +21159,7 @@
         <v>1</v>
       </c>
       <c r="F864" t="n">
-        <v>51.35</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="865">
@@ -21183,7 +21183,7 @@
         <v>1</v>
       </c>
       <c r="F865" t="n">
-        <v>49.17</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="866">
@@ -21207,7 +21207,7 @@
         <v>0</v>
       </c>
       <c r="F866" t="n">
-        <v>49.85</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="867">
@@ -21231,7 +21231,7 @@
         <v>0</v>
       </c>
       <c r="F867" t="n">
-        <v>54.23</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="868">
@@ -21255,7 +21255,7 @@
         <v>0</v>
       </c>
       <c r="F868" t="n">
-        <v>55.62</v>
+        <v>49.35</v>
       </c>
     </row>
     <row r="869">
@@ -21279,7 +21279,7 @@
         <v>0</v>
       </c>
       <c r="F869" t="n">
-        <v>56.01</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="870">
@@ -21303,7 +21303,7 @@
         <v>0</v>
       </c>
       <c r="F870" t="n">
-        <v>52.22</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="871">
@@ -21327,7 +21327,7 @@
         <v>0</v>
       </c>
       <c r="F871" t="n">
-        <v>55.5</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="872">
@@ -21351,7 +21351,7 @@
         <v>0</v>
       </c>
       <c r="F872" t="n">
-        <v>54.41</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="873">
@@ -21375,7 +21375,7 @@
         <v>0</v>
       </c>
       <c r="F873" t="n">
-        <v>52.63</v>
+        <v>52.21</v>
       </c>
     </row>
     <row r="874">
@@ -21399,7 +21399,7 @@
         <v>0</v>
       </c>
       <c r="F874" t="n">
-        <v>56.37</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="875">
@@ -21423,7 +21423,7 @@
         <v>0</v>
       </c>
       <c r="F875" t="n">
-        <v>56</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="876">
@@ -21447,7 +21447,7 @@
         <v>0</v>
       </c>
       <c r="F876" t="n">
-        <v>56.64</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="877">
@@ -21471,7 +21471,7 @@
         <v>0</v>
       </c>
       <c r="F877" t="n">
-        <v>59.77</v>
+        <v>50.97</v>
       </c>
     </row>
     <row r="878">
@@ -21495,7 +21495,7 @@
         <v>1</v>
       </c>
       <c r="F878" t="n">
-        <v>56.32</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="879">
@@ -21519,7 +21519,7 @@
         <v>1</v>
       </c>
       <c r="F879" t="n">
-        <v>56.13</v>
+        <v>56.51</v>
       </c>
     </row>
     <row r="880">
@@ -21543,7 +21543,7 @@
         <v>1</v>
       </c>
       <c r="F880" t="n">
-        <v>55.34</v>
+        <v>55.07</v>
       </c>
     </row>
     <row r="881">
@@ -21567,7 +21567,7 @@
         <v>1</v>
       </c>
       <c r="F881" t="n">
-        <v>57.79</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="882">
@@ -21591,7 +21591,7 @@
         <v>1</v>
       </c>
       <c r="F882" t="n">
-        <v>56.97</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="883">
@@ -21615,7 +21615,7 @@
         <v>1</v>
       </c>
       <c r="F883" t="n">
-        <v>54.51</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="884">
@@ -21639,7 +21639,7 @@
         <v>1</v>
       </c>
       <c r="F884" t="n">
-        <v>60.79</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="885">
@@ -21663,7 +21663,7 @@
         <v>1</v>
       </c>
       <c r="F885" t="n">
-        <v>58.77</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="886">
@@ -21687,7 +21687,7 @@
         <v>1</v>
       </c>
       <c r="F886" t="n">
-        <v>54.41</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="887">
@@ -21711,7 +21711,7 @@
         <v>1</v>
       </c>
       <c r="F887" t="n">
-        <v>55.69</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="888">
@@ -21735,7 +21735,7 @@
         <v>1</v>
       </c>
       <c r="F888" t="n">
-        <v>56.92</v>
+        <v>54.08</v>
       </c>
     </row>
     <row r="889">
@@ -21759,7 +21759,7 @@
         <v>1</v>
       </c>
       <c r="F889" t="n">
-        <v>58.58</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="890">
@@ -21783,7 +21783,7 @@
         <v>0</v>
       </c>
       <c r="F890" t="n">
-        <v>49.32</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="891">
@@ -21807,7 +21807,7 @@
         <v>0</v>
       </c>
       <c r="F891" t="n">
-        <v>51.56</v>
+        <v>52.19</v>
       </c>
     </row>
     <row r="892">
@@ -21831,7 +21831,7 @@
         <v>0</v>
       </c>
       <c r="F892" t="n">
-        <v>47.21</v>
+        <v>51.81</v>
       </c>
     </row>
     <row r="893">
@@ -21855,7 +21855,7 @@
         <v>0</v>
       </c>
       <c r="F893" t="n">
-        <v>47.62</v>
+        <v>54.59</v>
       </c>
     </row>
     <row r="894">
@@ -21879,7 +21879,7 @@
         <v>0</v>
       </c>
       <c r="F894" t="n">
-        <v>49.47</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="895">
@@ -21903,7 +21903,7 @@
         <v>0</v>
       </c>
       <c r="F895" t="n">
-        <v>46.93</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="896">
@@ -21927,7 +21927,7 @@
         <v>0</v>
       </c>
       <c r="F896" t="n">
-        <v>47.29</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="897">
@@ -21951,7 +21951,7 @@
         <v>0</v>
       </c>
       <c r="F897" t="n">
-        <v>49.12</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="898">
@@ -21975,7 +21975,7 @@
         <v>0</v>
       </c>
       <c r="F898" t="n">
-        <v>47.02</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="899">
@@ -21999,7 +21999,7 @@
         <v>0</v>
       </c>
       <c r="F899" t="n">
-        <v>46.15</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="900">
@@ -22023,7 +22023,7 @@
         <v>0</v>
       </c>
       <c r="F900" t="n">
-        <v>49.89</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="901">
@@ -22047,7 +22047,7 @@
         <v>0</v>
       </c>
       <c r="F901" t="n">
-        <v>46.2</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="902">
@@ -22071,7 +22071,7 @@
         <v>1</v>
       </c>
       <c r="F902" t="n">
-        <v>49.14</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="903">
@@ -22095,7 +22095,7 @@
         <v>1</v>
       </c>
       <c r="F903" t="n">
-        <v>49.31</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="904">
@@ -22119,7 +22119,7 @@
         <v>1</v>
       </c>
       <c r="F904" t="n">
-        <v>47.89</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="905">
@@ -22143,7 +22143,7 @@
         <v>1</v>
       </c>
       <c r="F905" t="n">
-        <v>51.45</v>
+        <v>55.71</v>
       </c>
     </row>
     <row r="906">
@@ -22167,7 +22167,7 @@
         <v>1</v>
       </c>
       <c r="F906" t="n">
-        <v>45.71</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="907">
@@ -22191,7 +22191,7 @@
         <v>1</v>
       </c>
       <c r="F907" t="n">
-        <v>51.11</v>
+        <v>56.53</v>
       </c>
     </row>
     <row r="908">
@@ -22215,7 +22215,7 @@
         <v>1</v>
       </c>
       <c r="F908" t="n">
-        <v>50.06</v>
+        <v>58.38</v>
       </c>
     </row>
     <row r="909">
@@ -22239,7 +22239,7 @@
         <v>1</v>
       </c>
       <c r="F909" t="n">
-        <v>53.01</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="910">
@@ -22263,7 +22263,7 @@
         <v>1</v>
       </c>
       <c r="F910" t="n">
-        <v>52.57</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="911">
@@ -22287,7 +22287,7 @@
         <v>1</v>
       </c>
       <c r="F911" t="n">
-        <v>55.15</v>
+        <v>62.46</v>
       </c>
     </row>
     <row r="912">
@@ -22311,7 +22311,7 @@
         <v>1</v>
       </c>
       <c r="F912" t="n">
-        <v>52.22</v>
+        <v>60.93</v>
       </c>
     </row>
     <row r="913">
@@ -22335,7 +22335,7 @@
         <v>1</v>
       </c>
       <c r="F913" t="n">
-        <v>50.48</v>
+        <v>60.39</v>
       </c>
     </row>
     <row r="914">
@@ -22359,7 +22359,7 @@
         <v>0</v>
       </c>
       <c r="F914" t="n">
-        <v>46.5</v>
+        <v>51.53</v>
       </c>
     </row>
     <row r="915">
@@ -22383,7 +22383,7 @@
         <v>0</v>
       </c>
       <c r="F915" t="n">
-        <v>51.52</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="916">
@@ -22407,7 +22407,7 @@
         <v>0</v>
       </c>
       <c r="F916" t="n">
-        <v>49.05</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="917">
@@ -22431,7 +22431,7 @@
         <v>0</v>
       </c>
       <c r="F917" t="n">
-        <v>53.78</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="918">
@@ -22455,7 +22455,7 @@
         <v>0</v>
       </c>
       <c r="F918" t="n">
-        <v>50.25</v>
+        <v>56.37</v>
       </c>
     </row>
     <row r="919">
@@ -22479,7 +22479,7 @@
         <v>0</v>
       </c>
       <c r="F919" t="n">
-        <v>54.76</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="920">
@@ -22503,7 +22503,7 @@
         <v>0</v>
       </c>
       <c r="F920" t="n">
-        <v>54.23</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="921">
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="F921" t="n">
-        <v>50.47</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="922">
@@ -22551,7 +22551,7 @@
         <v>0</v>
       </c>
       <c r="F922" t="n">
-        <v>54.26</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="923">
@@ -22575,7 +22575,7 @@
         <v>0</v>
       </c>
       <c r="F923" t="n">
-        <v>53.29</v>
+        <v>60.91</v>
       </c>
     </row>
     <row r="924">
@@ -22599,7 +22599,7 @@
         <v>0</v>
       </c>
       <c r="F924" t="n">
-        <v>54.68</v>
+        <v>61.39</v>
       </c>
     </row>
     <row r="925">
@@ -22623,7 +22623,7 @@
         <v>0</v>
       </c>
       <c r="F925" t="n">
-        <v>54.68</v>
+        <v>58.83</v>
       </c>
     </row>
     <row r="926">
@@ -22647,7 +22647,7 @@
         <v>1</v>
       </c>
       <c r="F926" t="n">
-        <v>53.55</v>
+        <v>57.68</v>
       </c>
     </row>
     <row r="927">
@@ -22671,7 +22671,7 @@
         <v>1</v>
       </c>
       <c r="F927" t="n">
-        <v>52.15</v>
+        <v>55.69</v>
       </c>
     </row>
     <row r="928">
@@ -22695,7 +22695,7 @@
         <v>1</v>
       </c>
       <c r="F928" t="n">
-        <v>56.67</v>
+        <v>55.56</v>
       </c>
     </row>
     <row r="929">
@@ -22719,7 +22719,7 @@
         <v>1</v>
       </c>
       <c r="F929" t="n">
-        <v>50.39</v>
+        <v>56.81</v>
       </c>
     </row>
     <row r="930">
@@ -22743,7 +22743,7 @@
         <v>1</v>
       </c>
       <c r="F930" t="n">
-        <v>56</v>
+        <v>58.52</v>
       </c>
     </row>
     <row r="931">
@@ -22767,7 +22767,7 @@
         <v>1</v>
       </c>
       <c r="F931" t="n">
-        <v>54.12</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="932">
@@ -22791,7 +22791,7 @@
         <v>1</v>
       </c>
       <c r="F932" t="n">
-        <v>54.56</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="933">
@@ -22815,7 +22815,7 @@
         <v>1</v>
       </c>
       <c r="F933" t="n">
-        <v>56.92</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="934">
@@ -22839,7 +22839,7 @@
         <v>1</v>
       </c>
       <c r="F934" t="n">
-        <v>56.84</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="935">
@@ -22863,7 +22863,7 @@
         <v>1</v>
       </c>
       <c r="F935" t="n">
-        <v>59.12</v>
+        <v>55.36</v>
       </c>
     </row>
     <row r="936">
@@ -22887,7 +22887,7 @@
         <v>1</v>
       </c>
       <c r="F936" t="n">
-        <v>58.21</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="937">
@@ -22911,7 +22911,7 @@
         <v>1</v>
       </c>
       <c r="F937" t="n">
-        <v>54.45</v>
+        <v>53.56</v>
       </c>
     </row>
     <row r="938">
@@ -22935,7 +22935,7 @@
         <v>0</v>
       </c>
       <c r="F938" t="n">
-        <v>50.55</v>
+        <v>47.92</v>
       </c>
     </row>
     <row r="939">
@@ -22959,7 +22959,7 @@
         <v>0</v>
       </c>
       <c r="F939" t="n">
-        <v>49.22</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="940">
@@ -22983,7 +22983,7 @@
         <v>0</v>
       </c>
       <c r="F940" t="n">
-        <v>49.02</v>
+        <v>47.59</v>
       </c>
     </row>
     <row r="941">
@@ -23007,7 +23007,7 @@
         <v>0</v>
       </c>
       <c r="F941" t="n">
-        <v>53.46</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="942">
@@ -23031,7 +23031,7 @@
         <v>0</v>
       </c>
       <c r="F942" t="n">
-        <v>52.76</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="943">
@@ -23055,7 +23055,7 @@
         <v>0</v>
       </c>
       <c r="F943" t="n">
-        <v>52.46</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="944">
@@ -23079,7 +23079,7 @@
         <v>0</v>
       </c>
       <c r="F944" t="n">
-        <v>50.98</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="945">
@@ -23103,7 +23103,7 @@
         <v>0</v>
       </c>
       <c r="F945" t="n">
-        <v>52.34</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="946">
@@ -23127,7 +23127,7 @@
         <v>0</v>
       </c>
       <c r="F946" t="n">
-        <v>50.65</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="947">
@@ -23151,7 +23151,7 @@
         <v>0</v>
       </c>
       <c r="F947" t="n">
-        <v>52.26</v>
+        <v>48.54</v>
       </c>
     </row>
     <row r="948">
@@ -23175,7 +23175,7 @@
         <v>0</v>
       </c>
       <c r="F948" t="n">
-        <v>53.71</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="949">
@@ -23199,7 +23199,7 @@
         <v>0</v>
       </c>
       <c r="F949" t="n">
-        <v>49.21</v>
+        <v>46.48</v>
       </c>
     </row>
     <row r="950">
@@ -23223,7 +23223,7 @@
         <v>1</v>
       </c>
       <c r="F950" t="n">
-        <v>50.88</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="951">
@@ -23247,7 +23247,7 @@
         <v>1</v>
       </c>
       <c r="F951" t="n">
-        <v>51.72</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="952">
@@ -23271,7 +23271,7 @@
         <v>1</v>
       </c>
       <c r="F952" t="n">
-        <v>53.42</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="953">
@@ -23295,7 +23295,7 @@
         <v>1</v>
       </c>
       <c r="F953" t="n">
-        <v>52.35</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="954">
@@ -23319,7 +23319,7 @@
         <v>1</v>
       </c>
       <c r="F954" t="n">
-        <v>53.63</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="955">
@@ -23343,7 +23343,7 @@
         <v>1</v>
       </c>
       <c r="F955" t="n">
-        <v>56.05</v>
+        <v>49.37</v>
       </c>
     </row>
     <row r="956">
@@ -23367,7 +23367,7 @@
         <v>1</v>
       </c>
       <c r="F956" t="n">
-        <v>53.99</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="957">
@@ -23391,7 +23391,7 @@
         <v>1</v>
       </c>
       <c r="F957" t="n">
-        <v>51.21</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="958">
@@ -23415,7 +23415,7 @@
         <v>1</v>
       </c>
       <c r="F958" t="n">
-        <v>53.1</v>
+        <v>54.92</v>
       </c>
     </row>
     <row r="959">
@@ -23439,7 +23439,7 @@
         <v>1</v>
       </c>
       <c r="F959" t="n">
-        <v>55.03</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="960">
@@ -23463,7 +23463,7 @@
         <v>1</v>
       </c>
       <c r="F960" t="n">
-        <v>52.51</v>
+        <v>53.73</v>
       </c>
     </row>
     <row r="961">
@@ -23487,7 +23487,7 @@
         <v>1</v>
       </c>
       <c r="F961" t="n">
-        <v>54.38</v>
+        <v>52.45</v>
       </c>
     </row>
   </sheetData>
@@ -23626,7 +23626,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pre-launch trends are parallel across groups; a common time trend affects both.</t>
+          <t>Pre-launch trends are parallel; a common time trend affects both; within-store revenue is serially correlated (AR1).</t>
         </is>
       </c>
     </row>
